--- a/data/k-props/2026-08-12.xlsx
+++ b/data/k-props/2026-08-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -190,24 +190,24 @@
     <t>Tampa Bay Rays @ Athletics</t>
   </si>
   <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
   </si>
   <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
     <t>Adrian Houser</t>
   </si>
   <si>
@@ -301,7 +301,13 @@
     <t>Bryan King</t>
   </si>
   <si>
-    <t>Role unknown</t>
+    <t>Opener</t>
+  </si>
+  <si>
+    <t>Ronel Blanco</t>
+  </si>
+  <si>
+    <t>Bulk pitcher</t>
   </si>
   <si>
     <t>José Soriano</t>
@@ -694,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ32"/>
+  <dimension ref="A1:AQ33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="43" width="16" customWidth="1"/>
@@ -845,10 +851,10 @@
         <v>112</v>
       </c>
       <c r="E2">
-        <v>-142</v>
+        <v>-129</v>
       </c>
       <c r="F2">
-        <v>6.26</v>
+        <v>6.11</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -857,7 +863,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>6.26</v>
+        <v>6.11</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -908,7 +914,7 @@
         <v>4.24</v>
       </c>
       <c r="AB2">
-        <v>1.225</v>
+        <v>1.1966</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -926,7 +932,7 @@
         <v>0.2379</v>
       </c>
       <c r="AH2">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI2">
         <v>1.0698</v>
@@ -958,10 +964,10 @@
         <v>-128</v>
       </c>
       <c r="E3">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F3">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -970,7 +976,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="L3" t="s">
         <v>52</v>
@@ -1021,7 +1027,7 @@
         <v>4.25</v>
       </c>
       <c r="AB3">
-        <v>0.894</v>
+        <v>0.8732</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -1039,7 +1045,7 @@
         <v>0.2101</v>
       </c>
       <c r="AH3">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI3">
         <v>0.9518</v>
@@ -1071,10 +1077,10 @@
         <v>-148</v>
       </c>
       <c r="E4">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F4">
-        <v>6.2</v>
+        <v>6.06</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1083,7 +1089,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.2</v>
+        <v>6.06</v>
       </c>
       <c r="L4" t="s">
         <v>46</v>
@@ -1107,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>0.3063</v>
@@ -1134,7 +1140,7 @@
         <v>3.91</v>
       </c>
       <c r="AB4">
-        <v>0.9177</v>
+        <v>0.8964</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1152,7 +1158,7 @@
         <v>0.2126</v>
       </c>
       <c r="AH4">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI4">
         <v>0.9321</v>
@@ -1181,13 +1187,13 @@
         <v>3.5</v>
       </c>
       <c r="D5">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="E5">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F5">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1196,7 +1202,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="L5" t="s">
         <v>52</v>
@@ -1220,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>0.2071</v>
@@ -1247,7 +1253,7 @@
         <v>4.26</v>
       </c>
       <c r="AB5">
-        <v>0.8235</v>
+        <v>0.8044</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1265,7 +1271,7 @@
         <v>0.2259</v>
       </c>
       <c r="AH5">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI5">
         <v>0.944</v>
@@ -1294,13 +1300,13 @@
         <v>5.5</v>
       </c>
       <c r="D6">
-        <v>112</v>
+        <v>-113</v>
       </c>
       <c r="E6">
-        <v>-142</v>
+        <v>115</v>
       </c>
       <c r="F6">
-        <v>7.04</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1309,7 +1315,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>7.62</v>
+        <v>8.28</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -1333,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>0.268</v>
@@ -1360,16 +1366,16 @@
         <v>3.9</v>
       </c>
       <c r="AB6">
-        <v>1.1669</v>
+        <v>1.2132</v>
       </c>
       <c r="AC6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD6">
-        <v>0.2571</v>
+        <v>0.2736</v>
       </c>
       <c r="AE6">
-        <v>0.2266</v>
+        <v>0.2465</v>
       </c>
       <c r="AF6">
         <v>9</v>
@@ -1378,19 +1384,19 @@
         <v>0.2171</v>
       </c>
       <c r="AH6">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI6">
-        <v>1.0377</v>
+        <v>1.0849</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM6">
         <v>-0.58</v>
@@ -1401,19 +1407,19 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>4.5</v>
       </c>
       <c r="D7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E7">
-        <v>-160</v>
+        <v>-147</v>
       </c>
       <c r="F7">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1422,7 +1428,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="s">
         <v>52</v>
@@ -1446,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>0.2636</v>
@@ -1473,16 +1479,16 @@
         <v>4.55</v>
       </c>
       <c r="AB7">
-        <v>0.8297</v>
+        <v>0.9169</v>
       </c>
       <c r="AC7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD7">
-        <v>0.1828</v>
+        <v>0.2068</v>
       </c>
       <c r="AE7">
-        <v>0.1778</v>
+        <v>0.2013</v>
       </c>
       <c r="AF7">
         <v>9</v>
@@ -1491,19 +1497,19 @@
         <v>0.192</v>
       </c>
       <c r="AH7">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI7">
-        <v>0.9086</v>
+        <v>0.88</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1514,19 +1520,19 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="E8">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F8">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1535,13 +1541,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="s">
         <v>52</v>
       </c>
       <c r="M8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N8">
         <v>825047</v>
@@ -1559,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>0.1541</v>
@@ -1586,37 +1592,37 @@
         <v>4.33</v>
       </c>
       <c r="AB8">
-        <v>1.0404</v>
+        <v>1.2301</v>
       </c>
       <c r="AC8" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD8">
-        <v>0.2292</v>
+        <v>0.2774</v>
       </c>
       <c r="AE8">
-        <v>0.2267</v>
+        <v>0.2232</v>
       </c>
       <c r="AF8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>0.2166</v>
       </c>
       <c r="AH8">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI8">
-        <v>1.0169</v>
+        <v>1.0549</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM8">
         <v>0</v>
@@ -1627,7 +1633,7 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -1636,10 +1642,10 @@
         <v>128</v>
       </c>
       <c r="E9">
-        <v>-164</v>
+        <v>-156</v>
       </c>
       <c r="F9">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1648,13 +1654,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="L9" t="s">
         <v>52</v>
       </c>
       <c r="M9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N9">
         <v>825047</v>
@@ -1672,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>0.1648</v>
@@ -1699,10 +1705,10 @@
         <v>4.37</v>
       </c>
       <c r="AB9">
-        <v>0.8027</v>
+        <v>0.7841</v>
       </c>
       <c r="AC9" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD9">
         <v>0.1768</v>
@@ -1717,7 +1723,7 @@
         <v>0.2002</v>
       </c>
       <c r="AH9">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI9">
         <v>0.9064</v>
@@ -1726,10 +1732,10 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1746,13 +1752,13 @@
         <v>2.5</v>
       </c>
       <c r="D10">
-        <v>-178</v>
+        <v>-180</v>
       </c>
       <c r="E10">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F10">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1761,7 +1767,7 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="L10" t="s">
         <v>52</v>
@@ -1785,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T10">
         <v>0.1533</v>
@@ -1812,10 +1818,10 @@
         <v>4.37</v>
       </c>
       <c r="AB10">
-        <v>0.9654</v>
+        <v>0.943</v>
       </c>
       <c r="AC10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD10">
         <v>0.2127</v>
@@ -1830,7 +1836,7 @@
         <v>0.2163</v>
       </c>
       <c r="AH10">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI10">
         <v>0.9721</v>
@@ -1839,10 +1845,10 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL10" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1856,16 +1862,16 @@
         <v>67</v>
       </c>
       <c r="C11">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D11">
-        <v>134</v>
+        <v>-143</v>
       </c>
       <c r="E11">
-        <v>-160</v>
+        <v>127</v>
       </c>
       <c r="F11">
-        <v>4.77</v>
+        <v>4.66</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1874,7 +1880,7 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>4.77</v>
+        <v>4.66</v>
       </c>
       <c r="L11" t="s">
         <v>52</v>
@@ -1898,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>0.203</v>
@@ -1925,10 +1931,10 @@
         <v>4.21</v>
       </c>
       <c r="AB11">
-        <v>1.031</v>
+        <v>1.007</v>
       </c>
       <c r="AC11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD11">
         <v>0.2271</v>
@@ -1943,7 +1949,7 @@
         <v>0.2157</v>
       </c>
       <c r="AH11">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI11">
         <v>0.9945</v>
@@ -1952,10 +1958,10 @@
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -1975,10 +1981,10 @@
         <v>-120</v>
       </c>
       <c r="E12">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F12">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1987,7 +1993,7 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="L12" t="s">
         <v>52</v>
@@ -2038,16 +2044,16 @@
         <v>4.19</v>
       </c>
       <c r="AB12">
-        <v>0.7103</v>
+        <v>0.7228</v>
       </c>
       <c r="AC12" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD12">
-        <v>0.1565</v>
+        <v>0.163</v>
       </c>
       <c r="AE12">
-        <v>0.1747</v>
+        <v>0.1842</v>
       </c>
       <c r="AF12">
         <v>9</v>
@@ -2056,19 +2062,19 @@
         <v>0.2193</v>
       </c>
       <c r="AH12">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI12">
-        <v>0.995</v>
+        <v>0.9807</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2082,16 +2088,16 @@
         <v>70</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D13">
+        <v>124</v>
+      </c>
+      <c r="E13">
         <v>-150</v>
       </c>
-      <c r="E13">
-        <v>127</v>
-      </c>
       <c r="F13">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2100,7 +2106,7 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="L13" t="s">
         <v>52</v>
@@ -2124,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>0.2239</v>
@@ -2151,10 +2157,10 @@
         <v>4.09</v>
       </c>
       <c r="AB13">
-        <v>0.9015</v>
+        <v>0.8806</v>
       </c>
       <c r="AC13" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD13">
         <v>0.1986</v>
@@ -2169,7 +2175,7 @@
         <v>0.2263</v>
       </c>
       <c r="AH13">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI13">
         <v>0.9855</v>
@@ -2178,10 +2184,10 @@
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2204,7 +2210,7 @@
         <v>-122</v>
       </c>
       <c r="F14">
-        <v>4.47</v>
+        <v>4.36</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2213,7 +2219,7 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.47</v>
+        <v>4.36</v>
       </c>
       <c r="L14" t="s">
         <v>52</v>
@@ -2237,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>0.1846</v>
@@ -2264,10 +2270,10 @@
         <v>4.38</v>
       </c>
       <c r="AB14">
-        <v>0.9832</v>
+        <v>0.9604</v>
       </c>
       <c r="AC14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD14">
         <v>0.2166</v>
@@ -2282,7 +2288,7 @@
         <v>0.2295</v>
       </c>
       <c r="AH14">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI14">
         <v>0.9526</v>
@@ -2291,10 +2297,10 @@
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2317,7 +2323,7 @@
         <v>-106</v>
       </c>
       <c r="F15">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2326,7 +2332,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="s">
         <v>52</v>
@@ -2350,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>0.1842</v>
@@ -2377,10 +2383,10 @@
         <v>4.29</v>
       </c>
       <c r="AB15">
-        <v>1.129</v>
+        <v>1.1028</v>
       </c>
       <c r="AC15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD15">
         <v>0.2487</v>
@@ -2395,7 +2401,7 @@
         <v>0.2104</v>
       </c>
       <c r="AH15">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI15">
         <v>0.9888</v>
@@ -2404,10 +2410,10 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2427,10 +2433,10 @@
         <v>124</v>
       </c>
       <c r="E16">
-        <v>-154</v>
+        <v>-150</v>
       </c>
       <c r="F16">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2439,7 +2445,7 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="L16" t="s">
         <v>52</v>
@@ -2463,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>0.1771</v>
@@ -2490,10 +2496,10 @@
         <v>4.29</v>
       </c>
       <c r="AB16">
-        <v>1.0197</v>
+        <v>0.996</v>
       </c>
       <c r="AC16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD16">
         <v>0.2246</v>
@@ -2508,7 +2514,7 @@
         <v>0.2367</v>
       </c>
       <c r="AH16">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI16">
         <v>1.01</v>
@@ -2517,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM16">
         <v>0</v>
@@ -2537,13 +2543,13 @@
         <v>4.5</v>
       </c>
       <c r="D17">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E17">
         <v>-131</v>
       </c>
       <c r="F17">
-        <v>3.91</v>
+        <v>3.82</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2552,7 +2558,7 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>3.91</v>
+        <v>3.82</v>
       </c>
       <c r="L17" t="s">
         <v>52</v>
@@ -2576,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>0.1849</v>
@@ -2603,10 +2609,10 @@
         <v>4.49</v>
       </c>
       <c r="AB17">
-        <v>0.9513</v>
+        <v>0.9293</v>
       </c>
       <c r="AC17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD17">
         <v>0.2096</v>
@@ -2621,7 +2627,7 @@
         <v>0.2351</v>
       </c>
       <c r="AH17">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI17">
         <v>1.0033</v>
@@ -2630,10 +2636,10 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2653,10 +2659,10 @@
         <v>-106</v>
       </c>
       <c r="E18">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="F18">
-        <v>6.02</v>
+        <v>5.88</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2665,10 +2671,10 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>6.02</v>
+        <v>5.88</v>
       </c>
       <c r="L18" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M18" t="s">
         <v>79</v>
@@ -2689,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>0.2582</v>
@@ -2716,10 +2722,10 @@
         <v>3.87</v>
       </c>
       <c r="AB18">
-        <v>1.2475</v>
+        <v>1.2186</v>
       </c>
       <c r="AC18" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD18">
         <v>0.2748</v>
@@ -2734,7 +2740,7 @@
         <v>0.2434</v>
       </c>
       <c r="AH18">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI18">
         <v>0.9967</v>
@@ -2743,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL18" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2769,7 +2775,7 @@
         <v>113</v>
       </c>
       <c r="F19">
-        <v>4.39</v>
+        <v>4.28</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2778,7 +2784,7 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>4.39</v>
+        <v>4.28</v>
       </c>
       <c r="L19" t="s">
         <v>52</v>
@@ -2802,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>0.2298</v>
@@ -2829,10 +2835,10 @@
         <v>4.35</v>
       </c>
       <c r="AB19">
-        <v>0.8822</v>
+        <v>0.8618</v>
       </c>
       <c r="AC19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD19">
         <v>0.1944</v>
@@ -2847,7 +2853,7 @@
         <v>0.2261</v>
       </c>
       <c r="AH19">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI19">
         <v>0.9889</v>
@@ -2856,10 +2862,10 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL19" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2879,7 +2885,7 @@
         <v>128</v>
       </c>
       <c r="E20">
-        <v>-143</v>
+        <v>-149</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2900,7 +2906,7 @@
         <v>45</v>
       </c>
       <c r="S20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20" t="s">
         <v>45</v>
@@ -2926,13 +2932,13 @@
         <v>4.5</v>
       </c>
       <c r="D21">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E21">
         <v>-125</v>
       </c>
       <c r="F21">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2941,7 +2947,7 @@
         <v>45</v>
       </c>
       <c r="K21">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="L21" t="s">
         <v>52</v>
@@ -2965,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>0.2547</v>
@@ -2992,10 +2998,10 @@
         <v>4.12</v>
       </c>
       <c r="AB21">
-        <v>0.8781</v>
+        <v>0.8577</v>
       </c>
       <c r="AC21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD21">
         <v>0.1934</v>
@@ -3010,7 +3016,7 @@
         <v>0.215</v>
       </c>
       <c r="AH21">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI21">
         <v>0.9791</v>
@@ -3019,10 +3025,10 @@
         <v>1</v>
       </c>
       <c r="AK21" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL21" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM21">
         <v>0</v>
@@ -3045,7 +3051,7 @@
         <v>-140</v>
       </c>
       <c r="F22">
-        <v>6.03</v>
+        <v>5.89</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -3054,10 +3060,10 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>6.03</v>
+        <v>5.89</v>
       </c>
       <c r="L22" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M22" t="s">
         <v>85</v>
@@ -3078,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>0.2295</v>
@@ -3105,10 +3111,10 @@
         <v>4.24</v>
       </c>
       <c r="AB22">
-        <v>1.1464</v>
+        <v>1.1197</v>
       </c>
       <c r="AC22" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD22">
         <v>0.2525</v>
@@ -3123,7 +3129,7 @@
         <v>0.2243</v>
       </c>
       <c r="AH22">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI22">
         <v>0.9975</v>
@@ -3132,10 +3138,10 @@
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL22" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM22">
         <v>0</v>
@@ -3155,7 +3161,7 @@
         <v>-109</v>
       </c>
       <c r="E23">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -3176,7 +3182,7 @@
         <v>45</v>
       </c>
       <c r="S23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23" t="s">
         <v>45</v>
@@ -3205,10 +3211,10 @@
         <v>-111</v>
       </c>
       <c r="E24">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="F24">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3217,7 +3223,7 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="L24" t="s">
         <v>52</v>
@@ -3241,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>0.1974</v>
@@ -3268,10 +3274,10 @@
         <v>4.45</v>
       </c>
       <c r="AB24">
-        <v>1.143</v>
+        <v>1.1165</v>
       </c>
       <c r="AC24" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD24">
         <v>0.2518</v>
@@ -3286,7 +3292,7 @@
         <v>0.2555</v>
       </c>
       <c r="AH24">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI24">
         <v>1.0521</v>
@@ -3295,10 +3301,10 @@
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL24" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM24">
         <v>0</v>
@@ -3321,7 +3327,7 @@
         <v>-155</v>
       </c>
       <c r="F25">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3330,7 +3336,7 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="L25" t="s">
         <v>52</v>
@@ -3354,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>0.1825</v>
@@ -3381,10 +3387,10 @@
         <v>4.49</v>
       </c>
       <c r="AB25">
-        <v>1.0101</v>
+        <v>0.9866</v>
       </c>
       <c r="AC25" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD25">
         <v>0.2225</v>
@@ -3399,7 +3405,7 @@
         <v>0.2371</v>
       </c>
       <c r="AH25">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI25">
         <v>1.0267</v>
@@ -3408,10 +3414,10 @@
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM25">
         <v>0</v>
@@ -3428,13 +3434,13 @@
         <v>4.5</v>
       </c>
       <c r="D26">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="F26">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3443,7 +3449,7 @@
         <v>45</v>
       </c>
       <c r="K26">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="L26" t="s">
         <v>52</v>
@@ -3467,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>0.1465</v>
@@ -3494,10 +3500,10 @@
         <v>4.23</v>
       </c>
       <c r="AB26">
-        <v>0.9482</v>
+        <v>0.9262</v>
       </c>
       <c r="AC26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD26">
         <v>0.2089</v>
@@ -3512,7 +3518,7 @@
         <v>0.2142</v>
       </c>
       <c r="AH26">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI26">
         <v>0.9653</v>
@@ -3521,10 +3527,10 @@
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM26">
         <v>0</v>
@@ -3541,10 +3547,10 @@
         <v>4.5</v>
       </c>
       <c r="D27">
-        <v>-113</v>
+        <v>-109</v>
       </c>
       <c r="E27">
-        <v>-110</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3565,7 +3571,7 @@
         <v>45</v>
       </c>
       <c r="S27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC27" t="s">
         <v>45</v>
@@ -3591,13 +3597,13 @@
         <v>3.5</v>
       </c>
       <c r="D28">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E28">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="F28">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="H28" t="s">
         <v>45</v>
@@ -3606,7 +3612,7 @@
         <v>45</v>
       </c>
       <c r="K28">
-        <v>3.74</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="s">
         <v>52</v>
@@ -3630,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="S28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>0.1558</v>
@@ -3657,10 +3663,10 @@
         <v>4.2</v>
       </c>
       <c r="AB28">
-        <v>1.2203</v>
+        <v>1.192</v>
       </c>
       <c r="AC28" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD28">
         <v>0.2688</v>
@@ -3675,7 +3681,7 @@
         <v>0.2508</v>
       </c>
       <c r="AH28">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI28">
         <v>1.0161</v>
@@ -3684,10 +3690,10 @@
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL28" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM28">
         <v>0</v>
@@ -3701,7 +3707,7 @@
         <v>95</v>
       </c>
       <c r="F29">
-        <v>3.57</v>
+        <v>1.06</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3710,7 +3716,7 @@
         <v>45</v>
       </c>
       <c r="K29">
-        <v>3.57</v>
+        <v>1.06</v>
       </c>
       <c r="L29" t="s">
         <v>52</v>
@@ -3725,13 +3731,13 @@
         <v>96</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -3746,37 +3752,37 @@
         <v>4.38</v>
       </c>
       <c r="AB29">
-        <v>0.9593</v>
+        <v>1.2106</v>
       </c>
       <c r="AC29" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD29">
-        <v>0.2113</v>
+        <v>0.273</v>
       </c>
       <c r="AE29">
-        <v>0.2155</v>
+        <v>0.2208</v>
       </c>
       <c r="AF29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG29">
         <v>0.2341</v>
       </c>
       <c r="AH29">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI29">
-        <v>1.019</v>
+        <v>1.0778</v>
       </c>
       <c r="AJ29" t="b">
         <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL29" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -3790,7 +3796,7 @@
         <v>97</v>
       </c>
       <c r="F30">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="H30" t="s">
         <v>45</v>
@@ -3799,88 +3805,88 @@
         <v>45</v>
       </c>
       <c r="K30">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="L30" t="s">
         <v>52</v>
       </c>
       <c r="M30" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="N30">
-        <v>822779</v>
+        <v>823187</v>
       </c>
       <c r="O30" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="P30">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
       <c r="R30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
       <c r="T30">
-        <v>0.2448</v>
+        <v>0.2099</v>
       </c>
       <c r="U30">
-        <v>0.2207</v>
+        <v>0.2099</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W30">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="X30">
-        <v>0.1759</v>
+        <v>0.2099</v>
       </c>
       <c r="Y30">
-        <v>0.351</v>
+        <v>0.288</v>
       </c>
       <c r="Z30" t="b">
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>4.16</v>
+        <v>4.19</v>
       </c>
       <c r="AB30">
-        <v>0.8507</v>
+        <v>1.2106</v>
       </c>
       <c r="AC30" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD30">
-        <v>0.1874</v>
+        <v>0.273</v>
       </c>
       <c r="AE30">
-        <v>0.1897</v>
+        <v>0.2208</v>
       </c>
       <c r="AF30">
         <v>9</v>
       </c>
       <c r="AG30">
-        <v>0.2181</v>
+        <v>0.2015</v>
       </c>
       <c r="AH30">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI30">
-        <v>0.9631</v>
+        <v>0.9583</v>
       </c>
       <c r="AJ30" t="b">
         <v>1</v>
       </c>
       <c r="AK30" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL30" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM30">
         <v>0</v>
@@ -3891,10 +3897,10 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31">
-        <v>3.84</v>
+        <v>4.08</v>
       </c>
       <c r="H31" t="s">
         <v>45</v>
@@ -3903,16 +3909,16 @@
         <v>45</v>
       </c>
       <c r="K31">
-        <v>3.84</v>
+        <v>4.08</v>
       </c>
       <c r="L31" t="s">
         <v>52</v>
       </c>
       <c r="M31" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N31">
-        <v>824883</v>
+        <v>822779</v>
       </c>
       <c r="O31" t="s">
         <v>48</v>
@@ -3930,61 +3936,61 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>0.1765</v>
+        <v>0.2448</v>
       </c>
       <c r="U31">
-        <v>0.1681</v>
+        <v>0.2207</v>
       </c>
       <c r="V31">
         <v>5</v>
       </c>
       <c r="W31">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="X31">
-        <v>0.1532</v>
+        <v>0.1759</v>
       </c>
       <c r="Y31">
-        <v>0.357</v>
+        <v>0.351</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>3.89</v>
+        <v>4.16</v>
       </c>
       <c r="AB31">
-        <v>1.0296</v>
+        <v>0.831</v>
       </c>
       <c r="AC31" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD31">
-        <v>0.2268</v>
+        <v>0.1874</v>
       </c>
       <c r="AE31">
-        <v>0.2191</v>
+        <v>0.1897</v>
       </c>
       <c r="AF31">
         <v>9</v>
       </c>
       <c r="AG31">
-        <v>0.2094</v>
+        <v>0.2181</v>
       </c>
       <c r="AH31">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI31">
-        <v>1.016</v>
+        <v>0.9631</v>
       </c>
       <c r="AJ31" t="b">
         <v>1</v>
       </c>
       <c r="AK31" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL31" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM31">
         <v>0</v>
@@ -3995,10 +4001,10 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>1.67</v>
+        <v>3.76</v>
       </c>
       <c r="H32" t="s">
         <v>45</v>
@@ -4007,25 +4013,25 @@
         <v>45</v>
       </c>
       <c r="K32">
-        <v>1.67</v>
+        <v>3.76</v>
       </c>
       <c r="L32" t="s">
         <v>52</v>
       </c>
       <c r="M32" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N32">
-        <v>823916</v>
+        <v>824883</v>
       </c>
       <c r="O32" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="P32">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
@@ -4034,63 +4040,167 @@
         <v>0</v>
       </c>
       <c r="T32">
-        <v>0.1917</v>
+        <v>0.1765</v>
       </c>
       <c r="U32">
-        <v>0.1921</v>
+        <v>0.1681</v>
       </c>
       <c r="V32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="X32">
-        <v>0.2</v>
+        <v>0.1532</v>
       </c>
       <c r="Y32">
-        <v>0.048</v>
+        <v>0.357</v>
       </c>
       <c r="Z32" t="b">
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>4.05</v>
+        <v>3.89</v>
       </c>
       <c r="AB32">
-        <v>1.2783</v>
+        <v>1.0057</v>
       </c>
       <c r="AC32" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AD32">
-        <v>0.2816</v>
+        <v>0.2268</v>
       </c>
       <c r="AE32">
-        <v>0.2198</v>
+        <v>0.2191</v>
       </c>
       <c r="AF32">
         <v>9</v>
       </c>
       <c r="AG32">
-        <v>0.1984</v>
+        <v>0.2094</v>
       </c>
       <c r="AH32">
-        <v>0.2203</v>
+        <v>0.2255</v>
       </c>
       <c r="AI32">
-        <v>1.0072</v>
+        <v>1.016</v>
       </c>
       <c r="AJ32" t="b">
         <v>1</v>
       </c>
       <c r="AK32" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AL32" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33">
+        <v>1.63</v>
+      </c>
+      <c r="H33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" t="s">
+        <v>45</v>
+      </c>
+      <c r="K33">
+        <v>1.63</v>
+      </c>
+      <c r="L33" t="s">
+        <v>52</v>
+      </c>
+      <c r="M33" t="s">
+        <v>91</v>
+      </c>
+      <c r="N33">
+        <v>823916</v>
+      </c>
+      <c r="O33" t="s">
+        <v>102</v>
+      </c>
+      <c r="P33">
+        <v>1.7</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0.1917</v>
+      </c>
+      <c r="U33">
+        <v>0.1921</v>
+      </c>
+      <c r="V33">
+        <v>1</v>
+      </c>
+      <c r="W33">
+        <v>10</v>
+      </c>
+      <c r="X33">
+        <v>0.2</v>
+      </c>
+      <c r="Y33">
+        <v>0.048</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>4.05</v>
+      </c>
+      <c r="AB33">
+        <v>1.2487</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD33">
+        <v>0.2816</v>
+      </c>
+      <c r="AE33">
+        <v>0.2198</v>
+      </c>
+      <c r="AF33">
+        <v>9</v>
+      </c>
+      <c r="AG33">
+        <v>0.1984</v>
+      </c>
+      <c r="AH33">
+        <v>0.2255</v>
+      </c>
+      <c r="AI33">
+        <v>1.0072</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM33">
         <v>0</v>
       </c>
     </row>

--- a/data/k-props/2026-08-12.xlsx
+++ b/data/k-props/2026-08-12.xlsx
@@ -1,17 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D817E65-43B8-442C-A4C4-E62D389B59E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="K-Props" state="visible" r:id="rId4"/>
+    <sheet name="K-Props" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="94">
   <si>
     <t>date</t>
   </si>
@@ -190,6 +207,12 @@
     <t>Tampa Bay Rays @ Athletics</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>projected_regulars</t>
+  </si>
+  <si>
     <t>Jack Perkins</t>
   </si>
   <si>
@@ -202,12 +225,6 @@
     <t>Ryan Feltner</t>
   </si>
   <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>projected_regulars</t>
-  </si>
-  <si>
     <t>Adrian Houser</t>
   </si>
   <si>
@@ -289,53 +306,31 @@
     <t>Kansas City Royals @ Los Angeles Dodgers</t>
   </si>
   <si>
-    <t>George Klassen</t>
-  </si>
-  <si>
     <t>Texas Rangers @ Los Angeles Angels</t>
   </si>
   <si>
     <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Bryan King</t>
-  </si>
-  <si>
-    <t>Opener</t>
-  </si>
-  <si>
-    <t>Ronel Blanco</t>
-  </si>
-  <si>
-    <t>Bulk pitcher</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Zac Thornton</t>
-  </si>
-  <si>
-    <t>Daniel Lynch IV</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -358,9 +353,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,9 +695,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ33"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AQ27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="43" width="16" customWidth="1"/>
   </cols>
@@ -853,8 +849,8 @@
       <c r="E2">
         <v>-129</v>
       </c>
-      <c r="F2">
-        <v>6.11</v>
+      <c r="F2" s="2">
+        <v>6.1827679431251754</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -863,7 +859,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>6.11</v>
+        <v>6.26</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -893,7 +889,7 @@
         <v>0.2</v>
       </c>
       <c r="U2">
-        <v>0.1962</v>
+        <v>0.19620000000000001</v>
       </c>
       <c r="V2">
         <v>5</v>
@@ -902,10 +898,10 @@
         <v>116</v>
       </c>
       <c r="X2">
-        <v>0.1897</v>
+        <v>0.18970000000000001</v>
       </c>
       <c r="Y2">
-        <v>0.367</v>
+        <v>0.36699999999999999</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -914,16 +910,16 @@
         <v>4.24</v>
       </c>
       <c r="AB2">
-        <v>1.1966</v>
+        <v>1.2250000000000001</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.2699</v>
+        <v>0.26989999999999997</v>
       </c>
       <c r="AE2">
-        <v>0.2579</v>
+        <v>0.25790000000000002</v>
       </c>
       <c r="AF2">
         <v>9</v>
@@ -932,10 +928,10 @@
         <v>0.2379</v>
       </c>
       <c r="AH2">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI2">
-        <v>1.0698</v>
+        <v>1.0698000000000001</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -966,8 +962,8 @@
       <c r="E3">
         <v>101</v>
       </c>
-      <c r="F3">
-        <v>4.69</v>
+      <c r="F3" s="2">
+        <v>4.8594294508315201</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -976,7 +972,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>4.69</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="s">
         <v>52</v>
@@ -1003,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="T3">
-        <v>0.2073</v>
+        <v>0.20730000000000001</v>
       </c>
       <c r="U3">
         <v>0.224</v>
@@ -1015,7 +1011,7 @@
         <v>119</v>
       </c>
       <c r="X3">
-        <v>0.2521</v>
+        <v>0.25209999999999999</v>
       </c>
       <c r="Y3">
         <v>0.373</v>
@@ -1027,28 +1023,28 @@
         <v>4.25</v>
       </c>
       <c r="AB3">
-        <v>0.8732</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
       </c>
       <c r="AD3">
-        <v>0.1969</v>
+        <v>0.19689999999999999</v>
       </c>
       <c r="AE3">
-        <v>0.1967</v>
+        <v>0.19670000000000001</v>
       </c>
       <c r="AF3">
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>0.2101</v>
+        <v>0.21010000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI3">
-        <v>0.9518</v>
+        <v>0.95179999999999998</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
@@ -1079,8 +1075,8 @@
       <c r="E4">
         <v>134</v>
       </c>
-      <c r="F4">
-        <v>6.06</v>
+      <c r="F4" s="2">
+        <v>6.4156687492360183</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1089,7 +1085,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.06</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="s">
         <v>46</v>
@@ -1113,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>0.3063</v>
+        <v>0.30630000000000002</v>
       </c>
       <c r="U4">
         <v>0.3196</v>
@@ -1128,10 +1124,10 @@
         <v>98</v>
       </c>
       <c r="X4">
-        <v>0.3469</v>
+        <v>0.34689999999999999</v>
       </c>
       <c r="Y4">
-        <v>0.329</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1140,13 +1136,13 @@
         <v>3.91</v>
       </c>
       <c r="AB4">
-        <v>0.8964</v>
+        <v>0.91769999999999996</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
       </c>
       <c r="AD4">
-        <v>0.2022</v>
+        <v>0.20219999999999999</v>
       </c>
       <c r="AE4">
         <v>0.1961</v>
@@ -1155,13 +1151,13 @@
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>0.2126</v>
+        <v>0.21260000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI4">
-        <v>0.9321</v>
+        <v>0.93210000000000004</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
@@ -1192,8 +1188,8 @@
       <c r="E5">
         <v>128</v>
       </c>
-      <c r="F5">
-        <v>3.71</v>
+      <c r="F5" s="2">
+        <v>3.9661122715329107</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1202,7 +1198,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="s">
         <v>52</v>
@@ -1217,7 +1213,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1226,13 +1222,13 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>0.2071</v>
+        <v>0.20710000000000001</v>
       </c>
       <c r="U5">
-        <v>0.2247</v>
+        <v>0.22470000000000001</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1244,7 +1240,7 @@
         <v>0.26</v>
       </c>
       <c r="Y5">
-        <v>0.333</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1253,13 +1249,13 @@
         <v>4.26</v>
       </c>
       <c r="AB5">
-        <v>0.8044</v>
+        <v>0.82350000000000001</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
       </c>
       <c r="AD5">
-        <v>0.1814</v>
+        <v>0.18140000000000001</v>
       </c>
       <c r="AE5">
         <v>0.1847</v>
@@ -1268,13 +1264,13 @@
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.2259</v>
+        <v>0.22589999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI5">
-        <v>0.944</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1305,8 +1301,8 @@
       <c r="E6">
         <v>115</v>
       </c>
-      <c r="F6">
-        <v>7.7</v>
+      <c r="F6" s="2">
+        <v>7.2342821068457246</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1315,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>8.28</v>
+        <v>7.62</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -1339,13 +1335,13 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6">
-        <v>0.268</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="U6">
-        <v>0.2854</v>
+        <v>0.28539999999999999</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1354,10 +1350,10 @@
         <v>107</v>
       </c>
       <c r="X6">
-        <v>0.3178</v>
+        <v>0.31780000000000003</v>
       </c>
       <c r="Y6">
-        <v>0.349</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1366,40 +1362,40 @@
         <v>3.9</v>
       </c>
       <c r="AB6">
-        <v>1.2132</v>
+        <v>1.1669</v>
       </c>
       <c r="AC6" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AD6">
-        <v>0.2736</v>
+        <v>0.2571</v>
       </c>
       <c r="AE6">
-        <v>0.2465</v>
+        <v>0.2266</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>0.2171</v>
+        <v>0.21709999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI6">
-        <v>1.0849</v>
+        <v>1.0377000000000001</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>-0.58</v>
+        <v>-0.57999999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1407,7 +1403,7 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1418,8 +1414,8 @@
       <c r="E7">
         <v>-147</v>
       </c>
-      <c r="F7">
-        <v>4.4</v>
+      <c r="F7" s="2">
+        <v>4.1986948721671471</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1428,7 +1424,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="L7" t="s">
         <v>52</v>
@@ -1443,7 +1439,7 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1452,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7">
         <v>0.2636</v>
@@ -1467,10 +1463,10 @@
         <v>108</v>
       </c>
       <c r="X7">
-        <v>0.2593</v>
+        <v>0.25929999999999997</v>
       </c>
       <c r="Y7">
-        <v>0.351</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1479,16 +1475,16 @@
         <v>4.55</v>
       </c>
       <c r="AB7">
-        <v>0.9169</v>
+        <v>0.82969999999999999</v>
       </c>
       <c r="AC7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AD7">
-        <v>0.2068</v>
+        <v>0.18279999999999999</v>
       </c>
       <c r="AE7">
-        <v>0.2013</v>
+        <v>0.17780000000000001</v>
       </c>
       <c r="AF7">
         <v>9</v>
@@ -1497,19 +1493,19 @@
         <v>0.192</v>
       </c>
       <c r="AH7">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI7">
-        <v>0.88</v>
+        <v>0.90859999999999996</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1520,7 +1516,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1531,8 +1527,8 @@
       <c r="E8">
         <v>112</v>
       </c>
-      <c r="F8">
-        <v>5.4</v>
+      <c r="F8" s="2">
+        <v>4.3701089018671402</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1541,13 +1537,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>5.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L8" t="s">
         <v>52</v>
       </c>
       <c r="M8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N8">
         <v>825047</v>
@@ -1565,13 +1561,13 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8">
-        <v>0.1541</v>
+        <v>0.15409999999999999</v>
       </c>
       <c r="U8">
-        <v>0.1683</v>
+        <v>0.16830000000000001</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1580,10 +1576,10 @@
         <v>108</v>
       </c>
       <c r="X8">
-        <v>0.1944</v>
+        <v>0.19439999999999999</v>
       </c>
       <c r="Y8">
-        <v>0.351</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1592,37 +1588,37 @@
         <v>4.33</v>
       </c>
       <c r="AB8">
-        <v>1.2301</v>
+        <v>1.0404</v>
       </c>
       <c r="AC8" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AD8">
-        <v>0.2774</v>
+        <v>0.22919999999999999</v>
       </c>
       <c r="AE8">
-        <v>0.2232</v>
+        <v>0.22670000000000001</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8">
-        <v>0.2166</v>
+        <v>0.21659999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI8">
-        <v>1.0549</v>
+        <v>1.0168999999999999</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM8">
         <v>0</v>
@@ -1633,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -1644,8 +1640,8 @@
       <c r="E9">
         <v>-156</v>
       </c>
-      <c r="F9">
-        <v>2.29</v>
+      <c r="F9" s="2">
+        <v>2.4278160127773987</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1654,13 +1650,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="L9" t="s">
         <v>52</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N9">
         <v>825047</v>
@@ -1678,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9">
         <v>0.1648</v>
@@ -1693,10 +1689,10 @@
         <v>114</v>
       </c>
       <c r="X9">
-        <v>0.1316</v>
+        <v>0.13159999999999999</v>
       </c>
       <c r="Y9">
-        <v>0.363</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1705,37 +1701,37 @@
         <v>4.37</v>
       </c>
       <c r="AB9">
-        <v>0.7841</v>
+        <v>0.80269999999999997</v>
       </c>
       <c r="AC9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD9">
-        <v>0.1768</v>
+        <v>0.17680000000000001</v>
       </c>
       <c r="AE9">
-        <v>0.1758</v>
+        <v>0.17580000000000001</v>
       </c>
       <c r="AF9">
         <v>9</v>
       </c>
       <c r="AG9">
-        <v>0.2002</v>
+        <v>0.20019999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI9">
-        <v>0.9064</v>
+        <v>0.90639999999999998</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1757,8 +1753,8 @@
       <c r="E10">
         <v>140</v>
       </c>
-      <c r="F10">
-        <v>3.33</v>
+      <c r="F10" s="2">
+        <v>3.4902871290320499</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1767,7 +1763,7 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="L10" t="s">
         <v>52</v>
@@ -1791,13 +1787,13 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T10">
-        <v>0.1533</v>
+        <v>0.15329999999999999</v>
       </c>
       <c r="U10">
-        <v>0.1763</v>
+        <v>0.17630000000000001</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1818,37 +1814,37 @@
         <v>4.37</v>
       </c>
       <c r="AB10">
-        <v>0.943</v>
+        <v>0.96540000000000004</v>
       </c>
       <c r="AC10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD10">
         <v>0.2127</v>
       </c>
       <c r="AE10">
-        <v>0.2008</v>
+        <v>0.20080000000000001</v>
       </c>
       <c r="AF10">
         <v>8</v>
       </c>
       <c r="AG10">
-        <v>0.2163</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="AH10">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI10">
-        <v>0.9721</v>
+        <v>0.97209999999999996</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1870,8 +1866,8 @@
       <c r="E11">
         <v>127</v>
       </c>
-      <c r="F11">
-        <v>4.66</v>
+      <c r="F11" s="2">
+        <v>4.9100581455049941</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1880,7 +1876,7 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>4.66</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="L11" t="s">
         <v>52</v>
@@ -1904,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T11">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="U11">
         <v>0.2006</v>
@@ -1922,7 +1918,7 @@
         <v>0.1966</v>
       </c>
       <c r="Y11">
-        <v>0.369</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -1931,16 +1927,16 @@
         <v>4.21</v>
       </c>
       <c r="AB11">
-        <v>1.007</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="AC11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD11">
         <v>0.2271</v>
       </c>
       <c r="AE11">
-        <v>0.2322</v>
+        <v>0.23219999999999999</v>
       </c>
       <c r="AF11">
         <v>9</v>
@@ -1949,19 +1945,19 @@
         <v>0.2157</v>
       </c>
       <c r="AH11">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI11">
-        <v>0.9945</v>
+        <v>0.99450000000000005</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -1983,8 +1979,8 @@
       <c r="E12">
         <v>110</v>
       </c>
-      <c r="F12">
-        <v>3.58</v>
+      <c r="F12" s="2">
+        <v>3.634309597473675</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1993,7 +1989,7 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="L12" t="s">
         <v>52</v>
@@ -2023,7 +2019,7 @@
         <v>0.2303</v>
       </c>
       <c r="U12">
-        <v>0.2302</v>
+        <v>0.23019999999999999</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -2035,46 +2031,46 @@
         <v>0.2301</v>
       </c>
       <c r="Y12">
-        <v>0.361</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="AB12">
-        <v>0.7228</v>
+        <v>0.71030000000000004</v>
       </c>
       <c r="AC12" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AD12">
-        <v>0.163</v>
+        <v>0.1565</v>
       </c>
       <c r="AE12">
-        <v>0.1842</v>
+        <v>0.17469999999999999</v>
       </c>
       <c r="AF12">
         <v>9</v>
       </c>
       <c r="AG12">
-        <v>0.2193</v>
+        <v>0.21929999999999999</v>
       </c>
       <c r="AH12">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI12">
-        <v>0.9807</v>
+        <v>0.995</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2096,8 +2092,8 @@
       <c r="E13">
         <v>-150</v>
       </c>
-      <c r="F13">
-        <v>4.22</v>
+      <c r="F13" s="2">
+        <v>4.4794020779858235</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2106,7 +2102,7 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="L13" t="s">
         <v>52</v>
@@ -2130,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>0.2239</v>
+        <v>0.22389999999999999</v>
       </c>
       <c r="U13">
         <v>0.2054</v>
@@ -2145,10 +2141,10 @@
         <v>125</v>
       </c>
       <c r="X13">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="Y13">
-        <v>0.385</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
@@ -2157,16 +2153,16 @@
         <v>4.09</v>
       </c>
       <c r="AB13">
-        <v>0.8806</v>
+        <v>0.90149999999999997</v>
       </c>
       <c r="AC13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD13">
         <v>0.1986</v>
       </c>
       <c r="AE13">
-        <v>0.1994</v>
+        <v>0.19939999999999999</v>
       </c>
       <c r="AF13">
         <v>9</v>
@@ -2175,19 +2171,19 @@
         <v>0.2263</v>
       </c>
       <c r="AH13">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI13">
-        <v>0.9855</v>
+        <v>0.98550000000000004</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2209,8 +2205,8 @@
       <c r="E14">
         <v>-122</v>
       </c>
-      <c r="F14">
-        <v>4.36</v>
+      <c r="F14" s="2">
+        <v>4.5722856847080715</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2219,7 +2215,7 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.36</v>
+        <v>4.47</v>
       </c>
       <c r="L14" t="s">
         <v>52</v>
@@ -2243,10 +2239,10 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>0.1846</v>
+        <v>0.18459999999999999</v>
       </c>
       <c r="U14">
         <v>0.1966</v>
@@ -2258,10 +2254,10 @@
         <v>115</v>
       </c>
       <c r="X14">
-        <v>0.2174</v>
+        <v>0.21740000000000001</v>
       </c>
       <c r="Y14">
-        <v>0.365</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2270,25 +2266,25 @@
         <v>4.38</v>
       </c>
       <c r="AB14">
-        <v>0.9604</v>
+        <v>0.98319999999999996</v>
       </c>
       <c r="AC14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD14">
-        <v>0.2166</v>
+        <v>0.21659999999999999</v>
       </c>
       <c r="AE14">
-        <v>0.2066</v>
+        <v>0.20660000000000001</v>
       </c>
       <c r="AF14">
         <v>9</v>
       </c>
       <c r="AG14">
-        <v>0.2295</v>
+        <v>0.22950000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI14">
         <v>0.9526</v>
@@ -2297,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2322,8 +2318,8 @@
       <c r="E15">
         <v>-106</v>
       </c>
-      <c r="F15">
-        <v>3.7</v>
+      <c r="F15" s="2">
+        <v>3.7638062617500929</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2332,7 +2328,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="L15" t="s">
         <v>52</v>
@@ -2356,13 +2352,13 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>0.1842</v>
       </c>
       <c r="U15">
-        <v>0.1683</v>
+        <v>0.16830000000000001</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -2374,7 +2370,7 @@
         <v>0.1389</v>
       </c>
       <c r="Y15">
-        <v>0.351</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
@@ -2383,16 +2379,16 @@
         <v>4.29</v>
       </c>
       <c r="AB15">
-        <v>1.1028</v>
+        <v>1.129</v>
       </c>
       <c r="AC15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD15">
         <v>0.2487</v>
       </c>
       <c r="AE15">
-        <v>0.2443</v>
+        <v>0.24429999999999999</v>
       </c>
       <c r="AF15">
         <v>9</v>
@@ -2401,19 +2397,19 @@
         <v>0.2104</v>
       </c>
       <c r="AH15">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI15">
-        <v>0.9888</v>
+        <v>0.98880000000000001</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2435,8 +2431,8 @@
       <c r="E16">
         <v>-150</v>
       </c>
-      <c r="F16">
-        <v>4.06</v>
+      <c r="F16" s="2">
+        <v>4.3434599737187751</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2445,7 +2441,7 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="L16" t="s">
         <v>52</v>
@@ -2460,7 +2456,7 @@
         <v>48</v>
       </c>
       <c r="P16">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2469,10 +2465,10 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>0.1771</v>
+        <v>0.17710000000000001</v>
       </c>
       <c r="U16">
         <v>0.1845</v>
@@ -2487,7 +2483,7 @@
         <v>0.2</v>
       </c>
       <c r="Y16">
-        <v>0.322</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
@@ -2496,25 +2492,25 @@
         <v>4.29</v>
       </c>
       <c r="AB16">
-        <v>0.996</v>
+        <v>1.0197000000000001</v>
       </c>
       <c r="AC16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD16">
-        <v>0.2246</v>
+        <v>0.22459999999999999</v>
       </c>
       <c r="AE16">
-        <v>0.2433</v>
+        <v>0.24329999999999999</v>
       </c>
       <c r="AF16">
         <v>8</v>
       </c>
       <c r="AG16">
-        <v>0.2367</v>
+        <v>0.23669999999999999</v>
       </c>
       <c r="AH16">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI16">
         <v>1.01</v>
@@ -2523,16 +2519,16 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -2548,8 +2544,8 @@
       <c r="E17">
         <v>-131</v>
       </c>
-      <c r="F17">
-        <v>3.82</v>
+      <c r="F17" s="2">
+        <v>3.8885214723809538</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2558,7 +2554,7 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>3.82</v>
+        <v>3.91</v>
       </c>
       <c r="L17" t="s">
         <v>52</v>
@@ -2582,13 +2578,13 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>0.1849</v>
+        <v>0.18490000000000001</v>
       </c>
       <c r="U17">
-        <v>0.1814</v>
+        <v>0.18140000000000001</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2600,7 +2596,7 @@
         <v>0.1754</v>
       </c>
       <c r="Y17">
-        <v>0.363</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
@@ -2609,16 +2605,16 @@
         <v>4.49</v>
       </c>
       <c r="AB17">
-        <v>0.9293</v>
+        <v>0.95130000000000003</v>
       </c>
       <c r="AC17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD17">
-        <v>0.2096</v>
+        <v>0.20960000000000001</v>
       </c>
       <c r="AE17">
-        <v>0.2156</v>
+        <v>0.21560000000000001</v>
       </c>
       <c r="AF17">
         <v>9</v>
@@ -2627,25 +2623,25 @@
         <v>0.2351</v>
       </c>
       <c r="AH17">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI17">
-        <v>1.0033</v>
+        <v>1.0033000000000001</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -2661,8 +2657,8 @@
       <c r="E18">
         <v>-115</v>
       </c>
-      <c r="F18">
-        <v>5.88</v>
+      <c r="F18" s="2">
+        <v>5.8706887444160278</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2671,10 +2667,10 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>5.88</v>
+        <v>6.02</v>
       </c>
       <c r="L18" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M18" t="s">
         <v>79</v>
@@ -2695,13 +2691,13 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>0.2582</v>
+        <v>0.25819999999999999</v>
       </c>
       <c r="U18">
-        <v>0.2194</v>
+        <v>0.21940000000000001</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2722,43 +2718,43 @@
         <v>3.87</v>
       </c>
       <c r="AB18">
-        <v>1.2186</v>
+        <v>1.2475000000000001</v>
       </c>
       <c r="AC18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD18">
-        <v>0.2748</v>
+        <v>0.27479999999999999</v>
       </c>
       <c r="AE18">
-        <v>0.2738</v>
+        <v>0.27379999999999999</v>
       </c>
       <c r="AF18">
         <v>9</v>
       </c>
       <c r="AG18">
-        <v>0.2434</v>
+        <v>0.24340000000000001</v>
       </c>
       <c r="AH18">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI18">
-        <v>0.9967</v>
+        <v>0.99670000000000003</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -2774,8 +2770,8 @@
       <c r="E19">
         <v>113</v>
       </c>
-      <c r="F19">
-        <v>4.28</v>
+      <c r="F19" s="2">
+        <v>4.5379989373023983</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2784,7 +2780,7 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>4.28</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="L19" t="s">
         <v>52</v>
@@ -2808,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>0.2298</v>
@@ -2823,7 +2819,7 @@
         <v>103</v>
       </c>
       <c r="X19">
-        <v>0.2136</v>
+        <v>0.21360000000000001</v>
       </c>
       <c r="Y19">
         <v>0.34</v>
@@ -2832,19 +2828,19 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="AB19">
-        <v>0.8618</v>
+        <v>0.88219999999999998</v>
       </c>
       <c r="AC19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD19">
-        <v>0.1944</v>
+        <v>0.19439999999999999</v>
       </c>
       <c r="AE19">
-        <v>0.1849</v>
+        <v>0.18490000000000001</v>
       </c>
       <c r="AF19">
         <v>9</v>
@@ -2853,7 +2849,7 @@
         <v>0.2261</v>
       </c>
       <c r="AH19">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI19">
         <v>0.9889</v>
@@ -2862,30 +2858,33 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D20">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E20">
-        <v>-149</v>
+        <v>-125</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4.928781580482978</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2893,52 +2892,112 @@
       <c r="J20" t="s">
         <v>45</v>
       </c>
+      <c r="K20">
+        <v>4.76</v>
+      </c>
       <c r="L20" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M20" t="s">
         <v>82</v>
       </c>
-      <c r="N20" t="s">
-        <v>45</v>
+      <c r="N20">
+        <v>822779</v>
       </c>
       <c r="O20" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P20">
+        <v>5.2</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="T20">
+        <v>0.25469999999999998</v>
+      </c>
+      <c r="U20">
+        <v>0.2611</v>
+      </c>
+      <c r="V20">
+        <v>5</v>
+      </c>
+      <c r="W20">
+        <v>87</v>
+      </c>
+      <c r="X20">
+        <v>0.27589999999999998</v>
+      </c>
+      <c r="Y20">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>4.12</v>
+      </c>
+      <c r="AB20">
+        <v>0.87809999999999999</v>
       </c>
       <c r="AC20" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>45</v>
+        <v>59</v>
+      </c>
+      <c r="AD20">
+        <v>0.19339999999999999</v>
+      </c>
+      <c r="AE20">
+        <v>0.1835</v>
+      </c>
+      <c r="AF20">
+        <v>9</v>
+      </c>
+      <c r="AG20">
+        <v>0.215</v>
+      </c>
+      <c r="AH20">
+        <v>0.2203</v>
+      </c>
+      <c r="AI20">
+        <v>0.97909999999999997</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AL20" t="s">
-        <v>45</v>
+        <v>60</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D21">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E21">
-        <v>-125</v>
-      </c>
-      <c r="F21">
-        <v>4.65</v>
+        <v>-140</v>
+      </c>
+      <c r="F21" s="2">
+        <v>6.0665901977500374</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2947,22 +3006,22 @@
         <v>45</v>
       </c>
       <c r="K21">
-        <v>4.65</v>
+        <v>6.03</v>
       </c>
       <c r="L21" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N21">
-        <v>822779</v>
+        <v>824883</v>
       </c>
       <c r="O21" t="s">
         <v>48</v>
       </c>
       <c r="P21">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -2971,87 +3030,87 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>0.2547</v>
+        <v>0.22950000000000001</v>
       </c>
       <c r="U21">
-        <v>0.2611</v>
+        <v>0.23480000000000001</v>
       </c>
       <c r="V21">
         <v>5</v>
       </c>
       <c r="W21">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="X21">
-        <v>0.2759</v>
+        <v>0.2437</v>
       </c>
       <c r="Y21">
-        <v>0.303</v>
+        <v>0.373</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="AB21">
-        <v>0.8577</v>
+        <v>1.1464000000000001</v>
       </c>
       <c r="AC21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD21">
-        <v>0.1934</v>
+        <v>0.2525</v>
       </c>
       <c r="AE21">
-        <v>0.1835</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="AF21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG21">
-        <v>0.215</v>
+        <v>0.2243</v>
       </c>
       <c r="AH21">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI21">
-        <v>0.9791</v>
+        <v>0.99750000000000005</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
       </c>
       <c r="AK21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C22">
         <v>5.5</v>
       </c>
       <c r="D22">
-        <v>129</v>
+        <v>-111</v>
       </c>
       <c r="E22">
-        <v>-140</v>
-      </c>
-      <c r="F22">
-        <v>5.89</v>
+        <v>-107</v>
+      </c>
+      <c r="F22" s="2">
+        <v>5.0908962815780567</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -3060,22 +3119,22 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>5.89</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="L22" t="s">
         <v>52</v>
       </c>
       <c r="M22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N22">
-        <v>824883</v>
+        <v>824562</v>
       </c>
       <c r="O22" t="s">
         <v>48</v>
       </c>
       <c r="P22">
-        <v>5.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -3084,84 +3143,87 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>0.2295</v>
+        <v>0.19739999999999999</v>
       </c>
       <c r="U22">
-        <v>0.2348</v>
+        <v>0.17849999999999999</v>
       </c>
       <c r="V22">
         <v>5</v>
       </c>
       <c r="W22">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="X22">
-        <v>0.2437</v>
+        <v>0.14749999999999999</v>
       </c>
       <c r="Y22">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>4.24</v>
+        <v>4.45</v>
       </c>
       <c r="AB22">
-        <v>1.1197</v>
+        <v>1.143</v>
       </c>
       <c r="AC22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD22">
-        <v>0.2525</v>
+        <v>0.25180000000000002</v>
       </c>
       <c r="AE22">
-        <v>0.2508</v>
+        <v>0.26750000000000002</v>
       </c>
       <c r="AF22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG22">
-        <v>0.2243</v>
+        <v>0.2555</v>
       </c>
       <c r="AH22">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI22">
-        <v>0.9975</v>
+        <v>1.0521</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C23">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D23">
-        <v>-109</v>
+        <v>134</v>
       </c>
       <c r="E23">
-        <v>102</v>
+        <v>-155</v>
+      </c>
+      <c r="F23" s="2">
+        <v>4.4071276909766404</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -3169,52 +3231,112 @@
       <c r="J23" t="s">
         <v>45</v>
       </c>
+      <c r="K23">
+        <v>4.26</v>
+      </c>
       <c r="L23" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M23" t="s">
-        <v>85</v>
-      </c>
-      <c r="N23" t="s">
-        <v>45</v>
+        <v>88</v>
+      </c>
+      <c r="N23">
+        <v>824562</v>
       </c>
       <c r="O23" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P23">
+        <v>4.8</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="T23">
+        <v>0.1825</v>
+      </c>
+      <c r="U23">
+        <v>0.1893</v>
+      </c>
+      <c r="V23">
+        <v>5</v>
+      </c>
+      <c r="W23">
+        <v>109</v>
+      </c>
+      <c r="X23">
+        <v>0.20180000000000001</v>
+      </c>
+      <c r="Y23">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>4.49</v>
+      </c>
+      <c r="AB23">
+        <v>1.0101</v>
       </c>
       <c r="AC23" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>45</v>
+        <v>59</v>
+      </c>
+      <c r="AD23">
+        <v>0.2225</v>
+      </c>
+      <c r="AE23">
+        <v>0.24249999999999999</v>
+      </c>
+      <c r="AF23">
+        <v>9</v>
+      </c>
+      <c r="AG23">
+        <v>0.23710000000000001</v>
+      </c>
+      <c r="AH23">
+        <v>0.2203</v>
+      </c>
+      <c r="AI23">
+        <v>1.0266999999999999</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>1</v>
       </c>
       <c r="AK23" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AL23" t="s">
-        <v>45</v>
+        <v>60</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C24">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>-111</v>
+        <v>131</v>
       </c>
       <c r="E24">
-        <v>-107</v>
-      </c>
-      <c r="F24">
-        <v>4.78</v>
+        <v>-166</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2.8748358220486776</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3223,22 +3345,22 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>4.78</v>
+        <v>2.73</v>
       </c>
       <c r="L24" t="s">
         <v>52</v>
       </c>
       <c r="M24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N24">
-        <v>824562</v>
+        <v>823916</v>
       </c>
       <c r="O24" t="s">
         <v>48</v>
       </c>
       <c r="P24">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -3247,87 +3369,87 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>0.1974</v>
+        <v>0.14649999999999999</v>
       </c>
       <c r="U24">
-        <v>0.1785</v>
+        <v>0.13930000000000001</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
       <c r="W24">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="X24">
-        <v>0.1475</v>
+        <v>0.12709999999999999</v>
       </c>
       <c r="Y24">
-        <v>0.379</v>
+        <v>0.371</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>4.45</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="AB24">
-        <v>1.1165</v>
+        <v>0.94820000000000004</v>
       </c>
       <c r="AC24" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD24">
-        <v>0.2518</v>
+        <v>0.2089</v>
       </c>
       <c r="AE24">
-        <v>0.2675</v>
+        <v>0.21240000000000001</v>
       </c>
       <c r="AF24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG24">
-        <v>0.2555</v>
+        <v>0.2142</v>
       </c>
       <c r="AH24">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI24">
-        <v>1.0521</v>
+        <v>0.96530000000000005</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL24" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C25">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D25">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>-155</v>
-      </c>
-      <c r="F25">
-        <v>4.16</v>
+        <v>-119</v>
+      </c>
+      <c r="F25" s="2">
+        <v>3.7774306226209875</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3336,22 +3458,22 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>4.16</v>
+        <v>3.74</v>
       </c>
       <c r="L25" t="s">
         <v>52</v>
       </c>
       <c r="M25" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="N25">
-        <v>824562</v>
+        <v>823994</v>
       </c>
       <c r="O25" t="s">
         <v>48</v>
       </c>
       <c r="P25">
-        <v>4.8</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3360,87 +3482,87 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>0.1825</v>
+        <v>0.15579999999999999</v>
       </c>
       <c r="U25">
-        <v>0.1893</v>
+        <v>0.15540000000000001</v>
       </c>
       <c r="V25">
         <v>5</v>
       </c>
       <c r="W25">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X25">
-        <v>0.2018</v>
+        <v>0.1545</v>
       </c>
       <c r="Y25">
-        <v>0.353</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="AB25">
-        <v>0.9866</v>
+        <v>1.2202999999999999</v>
       </c>
       <c r="AC25" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD25">
-        <v>0.2225</v>
+        <v>0.26879999999999998</v>
       </c>
       <c r="AE25">
-        <v>0.2425</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="AF25">
         <v>9</v>
       </c>
       <c r="AG25">
-        <v>0.2371</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="AH25">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI25">
-        <v>1.0267</v>
+        <v>1.0161</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL25" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C26">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D26">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E26">
-        <v>-166</v>
-      </c>
-      <c r="F26">
-        <v>2.67</v>
+        <v>-149</v>
+      </c>
+      <c r="F26" s="2">
+        <v>4.2632427752087452</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3449,22 +3571,22 @@
         <v>45</v>
       </c>
       <c r="K26">
-        <v>2.67</v>
+        <v>4.17</v>
       </c>
       <c r="L26" t="s">
         <v>52</v>
       </c>
       <c r="M26" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="N26">
-        <v>823916</v>
+        <v>822779</v>
       </c>
       <c r="O26" t="s">
         <v>48</v>
       </c>
       <c r="P26">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -3473,84 +3595,87 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>0.1465</v>
+        <v>0.24479999999999999</v>
       </c>
       <c r="U26">
-        <v>0.1393</v>
+        <v>0.22070000000000001</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="X26">
-        <v>0.1271</v>
+        <v>0.1759</v>
       </c>
       <c r="Y26">
-        <v>0.371</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
       <c r="AB26">
-        <v>0.9262</v>
+        <v>0.85070000000000001</v>
       </c>
       <c r="AC26" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="AD26">
-        <v>0.2089</v>
+        <v>0.18740000000000001</v>
       </c>
       <c r="AE26">
-        <v>0.2124</v>
+        <v>0.18970000000000001</v>
       </c>
       <c r="AF26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG26">
-        <v>0.2142</v>
+        <v>0.21809999999999999</v>
       </c>
       <c r="AH26">
-        <v>0.2255</v>
+        <v>0.2203</v>
       </c>
       <c r="AI26">
-        <v>0.9653</v>
+        <v>0.96309999999999996</v>
       </c>
       <c r="AJ26" t="b">
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AL26" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C27">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D27">
         <v>-109</v>
       </c>
       <c r="E27">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="F27" s="2">
+        <v>3.8800218899146075</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3558,654 +3683,96 @@
       <c r="J27" t="s">
         <v>45</v>
       </c>
+      <c r="K27">
+        <v>3.84</v>
+      </c>
       <c r="L27" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M27" t="s">
-        <v>93</v>
-      </c>
-      <c r="N27" t="s">
-        <v>45</v>
+        <v>85</v>
+      </c>
+      <c r="N27">
+        <v>824883</v>
       </c>
       <c r="O27" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P27">
+        <v>5.6</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="U27">
+        <v>0.1681</v>
+      </c>
+      <c r="V27">
+        <v>5</v>
+      </c>
+      <c r="W27">
+        <v>111</v>
+      </c>
+      <c r="X27">
+        <v>0.1532</v>
+      </c>
+      <c r="Y27">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>3.89</v>
+      </c>
+      <c r="AB27">
+        <v>1.0296000000000001</v>
       </c>
       <c r="AC27" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>45</v>
+        <v>59</v>
+      </c>
+      <c r="AD27">
+        <v>0.2268</v>
+      </c>
+      <c r="AE27">
+        <v>0.21909999999999999</v>
+      </c>
+      <c r="AF27">
+        <v>9</v>
+      </c>
+      <c r="AG27">
+        <v>0.2094</v>
+      </c>
+      <c r="AH27">
+        <v>0.2203</v>
+      </c>
+      <c r="AI27">
+        <v>1.016</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AL27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28">
-        <v>3.5</v>
-      </c>
-      <c r="D28">
-        <v>100</v>
-      </c>
-      <c r="E28">
-        <v>-119</v>
-      </c>
-      <c r="F28">
-        <v>3.65</v>
-      </c>
-      <c r="H28" t="s">
-        <v>45</v>
-      </c>
-      <c r="J28" t="s">
-        <v>45</v>
-      </c>
-      <c r="K28">
-        <v>3.65</v>
-      </c>
-      <c r="L28" t="s">
-        <v>52</v>
-      </c>
-      <c r="M28" t="s">
-        <v>93</v>
-      </c>
-      <c r="N28">
-        <v>823994</v>
-      </c>
-      <c r="O28" t="s">
-        <v>48</v>
-      </c>
-      <c r="P28">
-        <v>4.6</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>6</v>
-      </c>
-      <c r="T28">
-        <v>0.1558</v>
-      </c>
-      <c r="U28">
-        <v>0.1554</v>
-      </c>
-      <c r="V28">
-        <v>5</v>
-      </c>
-      <c r="W28">
-        <v>110</v>
-      </c>
-      <c r="X28">
-        <v>0.1545</v>
-      </c>
-      <c r="Y28">
-        <v>0.355</v>
-      </c>
-      <c r="Z28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>4.2</v>
-      </c>
-      <c r="AB28">
-        <v>1.192</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD28">
-        <v>0.2688</v>
-      </c>
-      <c r="AE28">
-        <v>0.264</v>
-      </c>
-      <c r="AF28">
-        <v>9</v>
-      </c>
-      <c r="AG28">
-        <v>0.2508</v>
-      </c>
-      <c r="AH28">
-        <v>0.2255</v>
-      </c>
-      <c r="AI28">
-        <v>1.0161</v>
-      </c>
-      <c r="AJ28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29">
-        <v>1.06</v>
-      </c>
-      <c r="H29" t="s">
-        <v>45</v>
-      </c>
-      <c r="J29" t="s">
-        <v>45</v>
-      </c>
-      <c r="K29">
-        <v>1.06</v>
-      </c>
-      <c r="L29" t="s">
-        <v>52</v>
-      </c>
-      <c r="M29" t="s">
-        <v>66</v>
-      </c>
-      <c r="N29">
-        <v>823187</v>
-      </c>
-      <c r="O29" t="s">
-        <v>96</v>
-      </c>
-      <c r="P29">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0.1852</v>
-      </c>
-      <c r="U29">
-        <v>0.1852</v>
-      </c>
-      <c r="AA29">
-        <v>4.38</v>
-      </c>
-      <c r="AB29">
-        <v>1.2106</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD29">
-        <v>0.273</v>
-      </c>
-      <c r="AE29">
-        <v>0.2208</v>
-      </c>
-      <c r="AF29">
-        <v>9</v>
-      </c>
-      <c r="AG29">
-        <v>0.2341</v>
-      </c>
-      <c r="AH29">
-        <v>0.2255</v>
-      </c>
-      <c r="AI29">
-        <v>1.0778</v>
-      </c>
-      <c r="AJ29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK29" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL29" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30">
-        <v>4.08</v>
-      </c>
-      <c r="H30" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30" t="s">
-        <v>45</v>
-      </c>
-      <c r="K30">
-        <v>4.08</v>
-      </c>
-      <c r="L30" t="s">
-        <v>52</v>
-      </c>
-      <c r="M30" t="s">
-        <v>66</v>
-      </c>
-      <c r="N30">
-        <v>823187</v>
-      </c>
-      <c r="O30" t="s">
-        <v>98</v>
-      </c>
-      <c r="P30">
-        <v>4</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>1</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0.2099</v>
-      </c>
-      <c r="U30">
-        <v>0.2099</v>
-      </c>
-      <c r="V30">
-        <v>4</v>
-      </c>
-      <c r="W30">
-        <v>81</v>
-      </c>
-      <c r="X30">
-        <v>0.2099</v>
-      </c>
-      <c r="Y30">
-        <v>0.288</v>
-      </c>
-      <c r="Z30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>4.19</v>
-      </c>
-      <c r="AB30">
-        <v>1.2106</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD30">
-        <v>0.273</v>
-      </c>
-      <c r="AE30">
-        <v>0.2208</v>
-      </c>
-      <c r="AF30">
-        <v>9</v>
-      </c>
-      <c r="AG30">
-        <v>0.2015</v>
-      </c>
-      <c r="AH30">
-        <v>0.2255</v>
-      </c>
-      <c r="AI30">
-        <v>0.9583</v>
-      </c>
-      <c r="AJ30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK30" t="s">
-        <v>50</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" t="s">
-        <v>99</v>
-      </c>
-      <c r="F31">
-        <v>4.08</v>
-      </c>
-      <c r="H31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J31" t="s">
-        <v>45</v>
-      </c>
-      <c r="K31">
-        <v>4.08</v>
-      </c>
-      <c r="L31" t="s">
-        <v>52</v>
-      </c>
-      <c r="M31" t="s">
-        <v>82</v>
-      </c>
-      <c r="N31">
-        <v>822779</v>
-      </c>
-      <c r="O31" t="s">
-        <v>48</v>
-      </c>
-      <c r="P31">
-        <v>5.6</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0.2448</v>
-      </c>
-      <c r="U31">
-        <v>0.2207</v>
-      </c>
-      <c r="V31">
-        <v>5</v>
-      </c>
-      <c r="W31">
-        <v>108</v>
-      </c>
-      <c r="X31">
-        <v>0.1759</v>
-      </c>
-      <c r="Y31">
-        <v>0.351</v>
-      </c>
-      <c r="Z31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>4.16</v>
-      </c>
-      <c r="AB31">
-        <v>0.831</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD31">
-        <v>0.1874</v>
-      </c>
-      <c r="AE31">
-        <v>0.1897</v>
-      </c>
-      <c r="AF31">
-        <v>9</v>
-      </c>
-      <c r="AG31">
-        <v>0.2181</v>
-      </c>
-      <c r="AH31">
-        <v>0.2255</v>
-      </c>
-      <c r="AI31">
-        <v>0.9631</v>
-      </c>
-      <c r="AJ31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK31" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32">
-        <v>3.76</v>
-      </c>
-      <c r="H32" t="s">
-        <v>45</v>
-      </c>
-      <c r="J32" t="s">
-        <v>45</v>
-      </c>
-      <c r="K32">
-        <v>3.76</v>
-      </c>
-      <c r="L32" t="s">
-        <v>52</v>
-      </c>
-      <c r="M32" t="s">
-        <v>85</v>
-      </c>
-      <c r="N32">
-        <v>824883</v>
-      </c>
-      <c r="O32" t="s">
-        <v>48</v>
-      </c>
-      <c r="P32">
-        <v>5.6</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0.1765</v>
-      </c>
-      <c r="U32">
-        <v>0.1681</v>
-      </c>
-      <c r="V32">
-        <v>5</v>
-      </c>
-      <c r="W32">
-        <v>111</v>
-      </c>
-      <c r="X32">
-        <v>0.1532</v>
-      </c>
-      <c r="Y32">
-        <v>0.357</v>
-      </c>
-      <c r="Z32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>3.89</v>
-      </c>
-      <c r="AB32">
-        <v>1.0057</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD32">
-        <v>0.2268</v>
-      </c>
-      <c r="AE32">
-        <v>0.2191</v>
-      </c>
-      <c r="AF32">
-        <v>9</v>
-      </c>
-      <c r="AG32">
-        <v>0.2094</v>
-      </c>
-      <c r="AH32">
-        <v>0.2255</v>
-      </c>
-      <c r="AI32">
-        <v>1.016</v>
-      </c>
-      <c r="AJ32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" t="s">
-        <v>101</v>
-      </c>
-      <c r="F33">
-        <v>1.63</v>
-      </c>
-      <c r="H33" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33" t="s">
-        <v>45</v>
-      </c>
-      <c r="K33">
-        <v>1.63</v>
-      </c>
-      <c r="L33" t="s">
-        <v>52</v>
-      </c>
-      <c r="M33" t="s">
-        <v>91</v>
-      </c>
-      <c r="N33">
-        <v>823916</v>
-      </c>
-      <c r="O33" t="s">
-        <v>102</v>
-      </c>
-      <c r="P33">
-        <v>1.7</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>1</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0.1917</v>
-      </c>
-      <c r="U33">
-        <v>0.1921</v>
-      </c>
-      <c r="V33">
-        <v>1</v>
-      </c>
-      <c r="W33">
-        <v>10</v>
-      </c>
-      <c r="X33">
-        <v>0.2</v>
-      </c>
-      <c r="Y33">
-        <v>0.048</v>
-      </c>
-      <c r="Z33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>4.05</v>
-      </c>
-      <c r="AB33">
-        <v>1.2487</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD33">
-        <v>0.2816</v>
-      </c>
-      <c r="AE33">
-        <v>0.2198</v>
-      </c>
-      <c r="AF33">
-        <v>9</v>
-      </c>
-      <c r="AG33">
-        <v>0.1984</v>
-      </c>
-      <c r="AH33">
-        <v>0.2255</v>
-      </c>
-      <c r="AI33">
-        <v>1.0072</v>
-      </c>
-      <c r="AJ33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK33" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM33">
+        <v>60</v>
+      </c>
+      <c r="AM27">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/k-props/2026-08-12.xlsx
+++ b/data/k-props/2026-08-12.xlsx
@@ -1,34 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D817E65-43B8-442C-A4C4-E62D389B59E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="K-Props" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="K-Props" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -162,33 +145,33 @@
     <t>2026-08-12</t>
   </si>
   <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
     <t>Zebby Matthews</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>Baltimore Orioles @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>posted</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
     <t>Zack Wheeler</t>
   </si>
   <si>
@@ -207,45 +190,57 @@
     <t>Tampa Bay Rays @ Athletics</t>
   </si>
   <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ Arizona Diamondbacks</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Bryan King</t>
+  </si>
+  <si>
+    <t>Houston Astros @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Opener</t>
+  </si>
+  <si>
+    <t>Ronel Blanco</t>
+  </si>
+  <si>
+    <t>Bulk pitcher</t>
+  </si>
+  <si>
+    <t>Adrian Houser</t>
+  </si>
+  <si>
+    <t>Dustin May</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ San Diego Padres</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Cleveland Guardians @ Detroit Tigers</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
   </si>
   <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ Arizona Diamondbacks</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Adrian Houser</t>
-  </si>
-  <si>
-    <t>Houston Astros @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ San Diego Padres</t>
-  </si>
-  <si>
-    <t>Dustin May</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Cleveland Guardians @ Detroit Tigers</t>
-  </si>
-  <si>
     <t>Framber Valdez</t>
   </si>
   <si>
@@ -273,64 +268,74 @@
     <t>Will Warren</t>
   </si>
   <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Zac Thornton</t>
+  </si>
+  <si>
+    <t>New York Mets @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Eric Lauer</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Los Angeles Angels</t>
+  </si>
+  <si>
     <t>Jose Soriano</t>
   </si>
   <si>
-    <t>Boston Red Sox @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>New York Mets @ Atlanta Braves</t>
-  </si>
-  <si>
     <t>Zach Thornton</t>
   </si>
   <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Eric Lauer</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
+    <t>George Klassen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -353,10 +358,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,9 +699,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AQ33"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="43" width="16" customWidth="1"/>
   </cols>
@@ -841,16 +845,16 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>112</v>
+        <v>-128</v>
       </c>
       <c r="E2">
-        <v>-129</v>
-      </c>
-      <c r="F2" s="2">
-        <v>6.1827679431251754</v>
+        <v>101</v>
+      </c>
+      <c r="F2">
+        <v>4.49</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -859,7 +863,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>6.26</v>
+        <v>4.49</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -886,52 +890,52 @@
         <v>4</v>
       </c>
       <c r="T2">
-        <v>0.2</v>
+        <v>0.2069</v>
       </c>
       <c r="U2">
-        <v>0.19620000000000001</v>
+        <v>0.2238</v>
       </c>
       <c r="V2">
         <v>5</v>
       </c>
       <c r="W2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="X2">
-        <v>0.18970000000000001</v>
+        <v>0.2521</v>
       </c>
       <c r="Y2">
-        <v>0.36699999999999999</v>
+        <v>0.373</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
       <c r="AB2">
-        <v>1.2250000000000001</v>
+        <v>0.8726</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.26989999999999997</v>
+        <v>0.1969</v>
       </c>
       <c r="AE2">
-        <v>0.25790000000000002</v>
+        <v>0.1967</v>
       </c>
       <c r="AF2">
         <v>9</v>
       </c>
       <c r="AG2">
-        <v>0.2379</v>
+        <v>0.2101</v>
       </c>
       <c r="AH2">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI2">
-        <v>1.0698000000000001</v>
+        <v>0.9518</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -954,16 +958,16 @@
         <v>51</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
-        <v>-128</v>
+        <v>112</v>
       </c>
       <c r="E3">
-        <v>101</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4.8594294508315201</v>
+        <v>-129</v>
+      </c>
+      <c r="F3">
+        <v>6.17</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -972,7 +976,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>4.8</v>
+        <v>6.17</v>
       </c>
       <c r="L3" t="s">
         <v>52</v>
@@ -987,7 +991,7 @@
         <v>48</v>
       </c>
       <c r="P3">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -999,22 +1003,22 @@
         <v>4</v>
       </c>
       <c r="T3">
-        <v>0.20730000000000001</v>
+        <v>0.2027</v>
       </c>
       <c r="U3">
-        <v>0.224</v>
+        <v>0.2086</v>
       </c>
       <c r="V3">
         <v>5</v>
       </c>
       <c r="W3">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="X3">
-        <v>0.25209999999999999</v>
+        <v>0.2211</v>
       </c>
       <c r="Y3">
-        <v>0.373</v>
+        <v>0.322</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -1023,28 +1027,28 @@
         <v>4.25</v>
       </c>
       <c r="AB3">
-        <v>0.89400000000000002</v>
+        <v>1.1957</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
       </c>
       <c r="AD3">
-        <v>0.19689999999999999</v>
+        <v>0.2699</v>
       </c>
       <c r="AE3">
-        <v>0.19670000000000001</v>
+        <v>0.2579</v>
       </c>
       <c r="AF3">
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>0.21010000000000001</v>
+        <v>0.2379</v>
       </c>
       <c r="AH3">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI3">
-        <v>0.95179999999999998</v>
+        <v>1.0698</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
@@ -1075,8 +1079,8 @@
       <c r="E4">
         <v>134</v>
       </c>
-      <c r="F4" s="2">
-        <v>6.4156687492360183</v>
+      <c r="F4">
+        <v>6.05</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1085,10 +1089,10 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="L4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M4" t="s">
         <v>54</v>
@@ -1109,10 +1113,10 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>0.30630000000000002</v>
+        <v>0.3063</v>
       </c>
       <c r="U4">
         <v>0.3196</v>
@@ -1124,10 +1128,10 @@
         <v>98</v>
       </c>
       <c r="X4">
-        <v>0.34689999999999999</v>
+        <v>0.3469</v>
       </c>
       <c r="Y4">
-        <v>0.32900000000000001</v>
+        <v>0.329</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1136,13 +1140,13 @@
         <v>3.91</v>
       </c>
       <c r="AB4">
-        <v>0.91769999999999996</v>
+        <v>0.8957</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
       </c>
       <c r="AD4">
-        <v>0.20219999999999999</v>
+        <v>0.2022</v>
       </c>
       <c r="AE4">
         <v>0.1961</v>
@@ -1151,13 +1155,13 @@
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>0.21260000000000001</v>
+        <v>0.2126</v>
       </c>
       <c r="AH4">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI4">
-        <v>0.93210000000000004</v>
+        <v>0.9321</v>
       </c>
       <c r="AJ4" t="b">
         <v>1</v>
@@ -1188,8 +1192,8 @@
       <c r="E5">
         <v>128</v>
       </c>
-      <c r="F5" s="2">
-        <v>3.9661122715329107</v>
+      <c r="F5">
+        <v>3.71</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1198,10 +1202,10 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="L5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M5" t="s">
         <v>54</v>
@@ -1213,7 +1217,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.0999999999999996</v>
+        <v>5.1</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1222,13 +1226,13 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>0.20710000000000001</v>
+        <v>0.2071</v>
       </c>
       <c r="U5">
-        <v>0.22470000000000001</v>
+        <v>0.2247</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1240,7 +1244,7 @@
         <v>0.26</v>
       </c>
       <c r="Y5">
-        <v>0.33300000000000002</v>
+        <v>0.333</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1249,13 +1253,13 @@
         <v>4.26</v>
       </c>
       <c r="AB5">
-        <v>0.82350000000000001</v>
+        <v>0.8038</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
       </c>
       <c r="AD5">
-        <v>0.18140000000000001</v>
+        <v>0.1814</v>
       </c>
       <c r="AE5">
         <v>0.1847</v>
@@ -1264,13 +1268,13 @@
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.22589999999999999</v>
+        <v>0.2259</v>
       </c>
       <c r="AH5">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI5">
-        <v>0.94399999999999995</v>
+        <v>0.944</v>
       </c>
       <c r="AJ5" t="b">
         <v>1</v>
@@ -1301,8 +1305,8 @@
       <c r="E6">
         <v>115</v>
       </c>
-      <c r="F6" s="2">
-        <v>7.2342821068457246</v>
+      <c r="F6">
+        <v>7.69</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1311,7 +1315,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>7.62</v>
+        <v>8.27</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -1335,13 +1339,13 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>0.26800000000000002</v>
+        <v>0.268</v>
       </c>
       <c r="U6">
-        <v>0.28539999999999999</v>
+        <v>0.2854</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1350,10 +1354,10 @@
         <v>107</v>
       </c>
       <c r="X6">
-        <v>0.31780000000000003</v>
+        <v>0.3178</v>
       </c>
       <c r="Y6">
-        <v>0.34899999999999998</v>
+        <v>0.349</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1362,40 +1366,40 @@
         <v>3.9</v>
       </c>
       <c r="AB6">
-        <v>1.1669</v>
+        <v>1.2123</v>
       </c>
       <c r="AC6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD6">
-        <v>0.2571</v>
+        <v>0.2736</v>
       </c>
       <c r="AE6">
-        <v>0.2266</v>
+        <v>0.2465</v>
       </c>
       <c r="AF6">
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>0.21709999999999999</v>
+        <v>0.2171</v>
       </c>
       <c r="AH6">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI6">
-        <v>1.0377000000000001</v>
+        <v>1.0849</v>
       </c>
       <c r="AJ6" t="b">
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM6">
-        <v>-0.57999999999999996</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
@@ -1403,7 +1407,7 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1414,8 +1418,8 @@
       <c r="E7">
         <v>-147</v>
       </c>
-      <c r="F7" s="2">
-        <v>4.1986948721671471</v>
+      <c r="F7">
+        <v>4.39</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1424,10 +1428,10 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.1100000000000003</v>
+        <v>4.39</v>
       </c>
       <c r="L7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M7" t="s">
         <v>58</v>
@@ -1439,7 +1443,7 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1448,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>0.2636</v>
@@ -1463,10 +1467,10 @@
         <v>108</v>
       </c>
       <c r="X7">
-        <v>0.25929999999999997</v>
+        <v>0.2593</v>
       </c>
       <c r="Y7">
-        <v>0.35099999999999998</v>
+        <v>0.351</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1475,16 +1479,16 @@
         <v>4.55</v>
       </c>
       <c r="AB7">
-        <v>0.82969999999999999</v>
+        <v>0.9162</v>
       </c>
       <c r="AC7" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD7">
-        <v>0.18279999999999999</v>
+        <v>0.2068</v>
       </c>
       <c r="AE7">
-        <v>0.17780000000000001</v>
+        <v>0.2013</v>
       </c>
       <c r="AF7">
         <v>9</v>
@@ -1493,19 +1497,19 @@
         <v>0.192</v>
       </c>
       <c r="AH7">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI7">
-        <v>0.90859999999999996</v>
+        <v>0.88</v>
       </c>
       <c r="AJ7" t="b">
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1516,19 +1520,19 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>-132</v>
+        <v>128</v>
       </c>
       <c r="E8">
-        <v>112</v>
-      </c>
-      <c r="F8" s="2">
-        <v>4.3701089018671402</v>
+        <v>-156</v>
+      </c>
+      <c r="F8">
+        <v>2.41</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1537,13 +1541,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>4.4000000000000004</v>
+        <v>2.41</v>
       </c>
       <c r="L8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N8">
         <v>825047</v>
@@ -1552,7 +1556,7 @@
         <v>48</v>
       </c>
       <c r="P8">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -1561,64 +1565,64 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>0.15409999999999999</v>
+        <v>0.1648</v>
       </c>
       <c r="U8">
-        <v>0.16830000000000001</v>
+        <v>0.1527</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="X8">
-        <v>0.19439999999999999</v>
+        <v>0.1316</v>
       </c>
       <c r="Y8">
-        <v>0.35099999999999998</v>
+        <v>0.363</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="AB8">
-        <v>1.0404</v>
+        <v>0.852</v>
       </c>
       <c r="AC8" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD8">
-        <v>0.22919999999999999</v>
+        <v>0.1923</v>
       </c>
       <c r="AE8">
-        <v>0.22670000000000001</v>
+        <v>0.1889</v>
       </c>
       <c r="AF8">
         <v>9</v>
       </c>
       <c r="AG8">
-        <v>0.21659999999999999</v>
+        <v>0.2002</v>
       </c>
       <c r="AH8">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI8">
-        <v>1.0168999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AJ8" t="b">
         <v>1</v>
       </c>
       <c r="AK8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM8">
         <v>0</v>
@@ -1629,19 +1633,19 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>128</v>
+        <v>-132</v>
       </c>
       <c r="E9">
-        <v>-156</v>
-      </c>
-      <c r="F9" s="2">
-        <v>2.4278160127773987</v>
+        <v>112</v>
+      </c>
+      <c r="F9">
+        <v>5.39</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1650,13 +1654,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>2.34</v>
+        <v>5.39</v>
       </c>
       <c r="L9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N9">
         <v>825047</v>
@@ -1665,7 +1669,7 @@
         <v>48</v>
       </c>
       <c r="P9">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1674,64 +1678,64 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>0.1648</v>
+        <v>0.1541</v>
       </c>
       <c r="U9">
-        <v>0.1527</v>
+        <v>0.1683</v>
       </c>
       <c r="V9">
         <v>5</v>
       </c>
       <c r="W9">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="X9">
-        <v>0.13159999999999999</v>
+        <v>0.1944</v>
       </c>
       <c r="Y9">
-        <v>0.36299999999999999</v>
+        <v>0.351</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="AB9">
-        <v>0.80269999999999997</v>
+        <v>1.2292</v>
       </c>
       <c r="AC9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD9">
-        <v>0.17680000000000001</v>
+        <v>0.2774</v>
       </c>
       <c r="AE9">
-        <v>0.17580000000000001</v>
+        <v>0.2232</v>
       </c>
       <c r="AF9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG9">
-        <v>0.20019999999999999</v>
+        <v>0.2166</v>
       </c>
       <c r="AH9">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI9">
-        <v>0.90639999999999998</v>
+        <v>1.0549</v>
       </c>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1742,19 +1746,10 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10">
-        <v>2.5</v>
-      </c>
-      <c r="D10">
-        <v>-180</v>
-      </c>
-      <c r="E10">
-        <v>140</v>
-      </c>
-      <c r="F10" s="2">
-        <v>3.4902871290320499</v>
+        <v>63</v>
+      </c>
+      <c r="F10">
+        <v>1.06</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1763,88 +1758,73 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>3.41</v>
+        <v>1.06</v>
       </c>
       <c r="L10" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N10">
         <v>823187</v>
       </c>
       <c r="O10" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="P10">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.15329999999999999</v>
+        <v>0.1852</v>
       </c>
       <c r="U10">
-        <v>0.17630000000000001</v>
-      </c>
-      <c r="V10">
-        <v>5</v>
-      </c>
-      <c r="W10">
-        <v>89</v>
-      </c>
-      <c r="X10">
-        <v>0.2472</v>
-      </c>
-      <c r="Y10">
-        <v>0.308</v>
-      </c>
-      <c r="Z10" t="b">
-        <v>1</v>
+        <v>0.1852</v>
       </c>
       <c r="AA10">
-        <v>4.37</v>
+        <v>4.38</v>
       </c>
       <c r="AB10">
-        <v>0.96540000000000004</v>
+        <v>1.2097</v>
       </c>
       <c r="AC10" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD10">
-        <v>0.2127</v>
+        <v>0.273</v>
       </c>
       <c r="AE10">
-        <v>0.20080000000000001</v>
+        <v>0.2208</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10">
-        <v>0.21629999999999999</v>
+        <v>0.2341</v>
       </c>
       <c r="AH10">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI10">
-        <v>0.97209999999999996</v>
+        <v>1.0778</v>
       </c>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1855,109 +1835,100 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11">
+        <v>4.08</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11">
+        <v>4.08</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11">
+        <v>823187</v>
+      </c>
+      <c r="O11" t="s">
         <v>67</v>
       </c>
-      <c r="C11">
-        <v>4.5</v>
-      </c>
-      <c r="D11">
-        <v>-143</v>
-      </c>
-      <c r="E11">
-        <v>127</v>
-      </c>
-      <c r="F11" s="2">
-        <v>4.9100581455049941</v>
-      </c>
-      <c r="H11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="L11" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11">
-        <v>823263</v>
-      </c>
-      <c r="O11" t="s">
-        <v>48</v>
-      </c>
       <c r="P11">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
       <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.20300000000000001</v>
+        <v>0.2099</v>
       </c>
       <c r="U11">
-        <v>0.2006</v>
+        <v>0.2099</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W11">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="X11">
-        <v>0.1966</v>
+        <v>0.2099</v>
       </c>
       <c r="Y11">
-        <v>0.36899999999999999</v>
+        <v>0.288</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="AB11">
-        <v>1.0309999999999999</v>
+        <v>1.2097</v>
       </c>
       <c r="AC11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD11">
-        <v>0.2271</v>
+        <v>0.273</v>
       </c>
       <c r="AE11">
-        <v>0.23219999999999999</v>
+        <v>0.2208</v>
       </c>
       <c r="AF11">
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>0.2157</v>
+        <v>0.2015</v>
       </c>
       <c r="AH11">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI11">
-        <v>0.99450000000000005</v>
+        <v>0.9583</v>
       </c>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
       <c r="AK11" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL11" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM11">
         <v>0</v>
@@ -1968,19 +1939,19 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="D12">
-        <v>-120</v>
+        <v>-180</v>
       </c>
       <c r="E12">
-        <v>110</v>
-      </c>
-      <c r="F12" s="2">
-        <v>3.634309597473675</v>
+        <v>140</v>
+      </c>
+      <c r="F12">
+        <v>2.76</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1989,22 +1960,22 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>3.56</v>
+        <v>2.76</v>
       </c>
       <c r="L12" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N12">
-        <v>823263</v>
+        <v>823187</v>
       </c>
       <c r="O12" t="s">
         <v>48</v>
       </c>
       <c r="P12">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -2013,64 +1984,64 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12">
-        <v>0.2303</v>
+        <v>0.1533</v>
       </c>
       <c r="U12">
-        <v>0.23019999999999999</v>
+        <v>0.1763</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="X12">
-        <v>0.2301</v>
+        <v>0.2472</v>
       </c>
       <c r="Y12">
-        <v>0.36099999999999999</v>
+        <v>0.308</v>
       </c>
       <c r="Z12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12">
-        <v>4.1900000000000004</v>
+        <v>4.37</v>
       </c>
       <c r="AB12">
-        <v>0.71030000000000004</v>
+        <v>0.8538</v>
       </c>
       <c r="AC12" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD12">
-        <v>0.1565</v>
+        <v>0.1927</v>
       </c>
       <c r="AE12">
-        <v>0.17469999999999999</v>
+        <v>0.1926</v>
       </c>
       <c r="AF12">
         <v>9</v>
       </c>
       <c r="AG12">
-        <v>0.21929999999999999</v>
+        <v>0.2163</v>
       </c>
       <c r="AH12">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI12">
-        <v>0.995</v>
+        <v>0.8914</v>
       </c>
       <c r="AJ12" t="b">
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -2081,43 +2052,43 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <v>4.5</v>
+      </c>
+      <c r="D13">
+        <v>-120</v>
+      </c>
+      <c r="E13">
+        <v>110</v>
+      </c>
+      <c r="F13">
+        <v>3.57</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13">
+        <v>3.57</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" t="s">
         <v>70</v>
       </c>
-      <c r="C13">
-        <v>5.5</v>
-      </c>
-      <c r="D13">
-        <v>124</v>
-      </c>
-      <c r="E13">
-        <v>-150</v>
-      </c>
-      <c r="F13" s="2">
-        <v>4.4794020779858235</v>
-      </c>
-      <c r="H13" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13">
-        <v>4.33</v>
-      </c>
-      <c r="L13" t="s">
-        <v>52</v>
-      </c>
-      <c r="M13" t="s">
-        <v>71</v>
-      </c>
       <c r="N13">
-        <v>824241</v>
+        <v>823263</v>
       </c>
       <c r="O13" t="s">
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2129,61 +2100,61 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>0.22389999999999999</v>
+        <v>0.2303</v>
       </c>
       <c r="U13">
-        <v>0.2054</v>
+        <v>0.2302</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="X13">
-        <v>0.17599999999999999</v>
+        <v>0.2301</v>
       </c>
       <c r="Y13">
-        <v>0.38500000000000001</v>
+        <v>0.361</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.09</v>
+        <v>4.19</v>
       </c>
       <c r="AB13">
-        <v>0.90149999999999997</v>
+        <v>0.7222</v>
       </c>
       <c r="AC13" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD13">
-        <v>0.1986</v>
+        <v>0.163</v>
       </c>
       <c r="AE13">
-        <v>0.19939999999999999</v>
+        <v>0.1842</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>0.2263</v>
+        <v>0.2193</v>
       </c>
       <c r="AH13">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI13">
-        <v>0.98550000000000004</v>
+        <v>0.9807</v>
       </c>
       <c r="AJ13" t="b">
         <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM13">
         <v>0</v>
@@ -2194,19 +2165,19 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14">
         <v>4.5</v>
       </c>
       <c r="D14">
-        <v>105</v>
+        <v>-143</v>
       </c>
       <c r="E14">
-        <v>-122</v>
-      </c>
-      <c r="F14" s="2">
-        <v>4.5722856847080715</v>
+        <v>127</v>
+      </c>
+      <c r="F14">
+        <v>4.67</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2215,16 +2186,16 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.47</v>
+        <v>4.67</v>
       </c>
       <c r="L14" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N14">
-        <v>824241</v>
+        <v>823263</v>
       </c>
       <c r="O14" t="s">
         <v>48</v>
@@ -2239,64 +2210,64 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>0.18459999999999999</v>
+        <v>0.203</v>
       </c>
       <c r="U14">
-        <v>0.1966</v>
+        <v>0.2006</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="X14">
-        <v>0.21740000000000001</v>
+        <v>0.1966</v>
       </c>
       <c r="Y14">
-        <v>0.36499999999999999</v>
+        <v>0.369</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
       <c r="AB14">
-        <v>0.98319999999999996</v>
+        <v>1.049</v>
       </c>
       <c r="AC14" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="AD14">
-        <v>0.21659999999999999</v>
+        <v>0.2368</v>
       </c>
       <c r="AE14">
-        <v>0.20660000000000001</v>
+        <v>0.2266</v>
       </c>
       <c r="AF14">
         <v>9</v>
       </c>
       <c r="AG14">
-        <v>0.22950000000000001</v>
+        <v>0.2157</v>
       </c>
       <c r="AH14">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI14">
-        <v>0.9526</v>
+        <v>0.9557</v>
       </c>
       <c r="AJ14" t="b">
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL14" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2307,43 +2278,43 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15">
+        <v>5.5</v>
+      </c>
+      <c r="D15">
+        <v>124</v>
+      </c>
+      <c r="E15">
+        <v>-150</v>
+      </c>
+      <c r="F15">
+        <v>4.22</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15">
+        <v>4.22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" t="s">
         <v>73</v>
       </c>
-      <c r="C15">
-        <v>3.5</v>
-      </c>
-      <c r="D15">
-        <v>-105</v>
-      </c>
-      <c r="E15">
-        <v>-106</v>
-      </c>
-      <c r="F15" s="2">
-        <v>3.7638062617500929</v>
-      </c>
-      <c r="H15" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15">
-        <v>3.79</v>
-      </c>
-      <c r="L15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15" t="s">
-        <v>74</v>
-      </c>
       <c r="N15">
-        <v>823833</v>
+        <v>824241</v>
       </c>
       <c r="O15" t="s">
         <v>48</v>
       </c>
       <c r="P15">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2352,64 +2323,64 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15">
-        <v>0.1842</v>
+        <v>0.2239</v>
       </c>
       <c r="U15">
-        <v>0.16830000000000001</v>
+        <v>0.2054</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="X15">
-        <v>0.1389</v>
+        <v>0.176</v>
       </c>
       <c r="Y15">
-        <v>0.35099999999999998</v>
+        <v>0.385</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>4.29</v>
+        <v>4.09</v>
       </c>
       <c r="AB15">
-        <v>1.129</v>
+        <v>0.8799</v>
       </c>
       <c r="AC15" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD15">
-        <v>0.2487</v>
+        <v>0.1986</v>
       </c>
       <c r="AE15">
-        <v>0.24429999999999999</v>
+        <v>0.1994</v>
       </c>
       <c r="AF15">
         <v>9</v>
       </c>
       <c r="AG15">
-        <v>0.2104</v>
+        <v>0.2263</v>
       </c>
       <c r="AH15">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI15">
-        <v>0.98880000000000001</v>
+        <v>0.9855</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL15" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2420,19 +2391,19 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16">
         <v>4.5</v>
       </c>
       <c r="D16">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E16">
-        <v>-150</v>
-      </c>
-      <c r="F16" s="2">
-        <v>4.3434599737187751</v>
+        <v>-122</v>
+      </c>
+      <c r="F16">
+        <v>4.36</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2441,22 +2412,22 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.16</v>
+        <v>4.36</v>
       </c>
       <c r="L16" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N16">
-        <v>823833</v>
+        <v>824241</v>
       </c>
       <c r="O16" t="s">
         <v>48</v>
       </c>
       <c r="P16">
-        <v>5.0999999999999996</v>
+        <v>5.5</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -2465,87 +2436,87 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>0.17710000000000001</v>
+        <v>0.1846</v>
       </c>
       <c r="U16">
-        <v>0.1845</v>
+        <v>0.1966</v>
       </c>
       <c r="V16">
         <v>5</v>
       </c>
       <c r="W16">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="X16">
-        <v>0.2</v>
+        <v>0.2174</v>
       </c>
       <c r="Y16">
-        <v>0.32200000000000001</v>
+        <v>0.365</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AB16">
-        <v>1.0197000000000001</v>
+        <v>0.9597</v>
       </c>
       <c r="AC16" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD16">
-        <v>0.22459999999999999</v>
+        <v>0.2166</v>
       </c>
       <c r="AE16">
-        <v>0.24329999999999999</v>
+        <v>0.2066</v>
       </c>
       <c r="AF16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG16">
-        <v>0.23669999999999999</v>
+        <v>0.2295</v>
       </c>
       <c r="AH16">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI16">
-        <v>1.01</v>
+        <v>0.9526</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D17">
-        <v>115</v>
+        <v>-105</v>
       </c>
       <c r="E17">
-        <v>-131</v>
-      </c>
-      <c r="F17" s="2">
-        <v>3.8885214723809538</v>
+        <v>-106</v>
+      </c>
+      <c r="F17">
+        <v>3.7</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2554,22 +2525,22 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="L17" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N17">
-        <v>822698</v>
+        <v>823833</v>
       </c>
       <c r="O17" t="s">
         <v>48</v>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -2578,87 +2549,87 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>0.18490000000000001</v>
+        <v>0.1842</v>
       </c>
       <c r="U17">
-        <v>0.18140000000000001</v>
+        <v>0.1683</v>
       </c>
       <c r="V17">
         <v>5</v>
       </c>
       <c r="W17">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="X17">
-        <v>0.1754</v>
+        <v>0.1389</v>
       </c>
       <c r="Y17">
-        <v>0.36299999999999999</v>
+        <v>0.351</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>4.49</v>
+        <v>4.29</v>
       </c>
       <c r="AB17">
-        <v>0.95130000000000003</v>
+        <v>1.1019</v>
       </c>
       <c r="AC17" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD17">
-        <v>0.20960000000000001</v>
+        <v>0.2487</v>
       </c>
       <c r="AE17">
-        <v>0.21560000000000001</v>
+        <v>0.2443</v>
       </c>
       <c r="AF17">
         <v>9</v>
       </c>
       <c r="AG17">
-        <v>0.2351</v>
+        <v>0.2104</v>
       </c>
       <c r="AH17">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI17">
-        <v>1.0033000000000001</v>
+        <v>0.9888</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL17" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-106</v>
+        <v>124</v>
       </c>
       <c r="E18">
-        <v>-115</v>
-      </c>
-      <c r="F18" s="2">
-        <v>5.8706887444160278</v>
+        <v>-150</v>
+      </c>
+      <c r="F18">
+        <v>4.06</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2667,22 +2638,22 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>6.02</v>
+        <v>4.06</v>
       </c>
       <c r="L18" t="s">
         <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N18">
-        <v>823511</v>
+        <v>823833</v>
       </c>
       <c r="O18" t="s">
         <v>48</v>
       </c>
       <c r="P18">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
@@ -2691,70 +2662,70 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>0.25819999999999999</v>
+        <v>0.1771</v>
       </c>
       <c r="U18">
-        <v>0.21940000000000001</v>
+        <v>0.1845</v>
       </c>
       <c r="V18">
         <v>5</v>
       </c>
       <c r="W18">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="X18">
-        <v>0.1429</v>
+        <v>0.2</v>
       </c>
       <c r="Y18">
-        <v>0.373</v>
+        <v>0.322</v>
       </c>
       <c r="Z18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>3.87</v>
+        <v>4.29</v>
       </c>
       <c r="AB18">
-        <v>1.2475000000000001</v>
+        <v>0.9953</v>
       </c>
       <c r="AC18" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD18">
-        <v>0.27479999999999999</v>
+        <v>0.2246</v>
       </c>
       <c r="AE18">
-        <v>0.27379999999999999</v>
+        <v>0.2433</v>
       </c>
       <c r="AF18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG18">
-        <v>0.24340000000000001</v>
+        <v>0.2367</v>
       </c>
       <c r="AH18">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI18">
-        <v>0.99670000000000003</v>
+        <v>1.01</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL18" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -2765,13 +2736,13 @@
         <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-132</v>
+        <v>115</v>
       </c>
       <c r="E19">
-        <v>113</v>
-      </c>
-      <c r="F19" s="2">
-        <v>4.5379989373023983</v>
+        <v>-131</v>
+      </c>
+      <c r="F19">
+        <v>3.81</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2780,22 +2751,22 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>4.3899999999999997</v>
+        <v>3.81</v>
       </c>
       <c r="L19" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N19">
-        <v>823511</v>
+        <v>822698</v>
       </c>
       <c r="O19" t="s">
         <v>48</v>
       </c>
       <c r="P19">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -2804,111 +2775,111 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>0.2298</v>
+        <v>0.1849</v>
       </c>
       <c r="U19">
-        <v>0.2243</v>
+        <v>0.1814</v>
       </c>
       <c r="V19">
         <v>5</v>
       </c>
       <c r="W19">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="X19">
-        <v>0.21360000000000001</v>
+        <v>0.1754</v>
       </c>
       <c r="Y19">
-        <v>0.34</v>
+        <v>0.363</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>4.3499999999999996</v>
+        <v>4.49</v>
       </c>
       <c r="AB19">
-        <v>0.88219999999999998</v>
+        <v>0.9286</v>
       </c>
       <c r="AC19" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD19">
-        <v>0.19439999999999999</v>
+        <v>0.2096</v>
       </c>
       <c r="AE19">
-        <v>0.18490000000000001</v>
+        <v>0.2156</v>
       </c>
       <c r="AF19">
         <v>9</v>
       </c>
       <c r="AG19">
-        <v>0.2261</v>
+        <v>0.2351</v>
       </c>
       <c r="AH19">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI19">
-        <v>0.9889</v>
+        <v>1.0033</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>43</v>
       </c>
       <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20">
+        <v>5.5</v>
+      </c>
+      <c r="D20">
+        <v>-106</v>
+      </c>
+      <c r="E20">
+        <v>-115</v>
+      </c>
+      <c r="F20">
+        <v>5.87</v>
+      </c>
+      <c r="H20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20">
+        <v>5.87</v>
+      </c>
+      <c r="L20" t="s">
+        <v>46</v>
+      </c>
+      <c r="M20" t="s">
         <v>83</v>
       </c>
-      <c r="C20">
-        <v>4.5</v>
-      </c>
-      <c r="D20">
-        <v>110</v>
-      </c>
-      <c r="E20">
-        <v>-125</v>
-      </c>
-      <c r="F20" s="2">
-        <v>4.928781580482978</v>
-      </c>
-      <c r="H20" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20">
-        <v>4.76</v>
-      </c>
-      <c r="L20" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" t="s">
-        <v>82</v>
-      </c>
       <c r="N20">
-        <v>822779</v>
+        <v>823511</v>
       </c>
       <c r="O20" t="s">
         <v>48</v>
       </c>
       <c r="P20">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -2917,70 +2888,70 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>0.25469999999999998</v>
+        <v>0.2582</v>
       </c>
       <c r="U20">
-        <v>0.2611</v>
+        <v>0.2194</v>
       </c>
       <c r="V20">
         <v>5</v>
       </c>
       <c r="W20">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="X20">
-        <v>0.27589999999999998</v>
+        <v>0.1429</v>
       </c>
       <c r="Y20">
-        <v>0.30299999999999999</v>
+        <v>0.373</v>
       </c>
       <c r="Z20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20">
-        <v>4.12</v>
+        <v>3.87</v>
       </c>
       <c r="AB20">
-        <v>0.87809999999999999</v>
+        <v>1.2176</v>
       </c>
       <c r="AC20" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD20">
-        <v>0.19339999999999999</v>
+        <v>0.2748</v>
       </c>
       <c r="AE20">
-        <v>0.1835</v>
+        <v>0.2738</v>
       </c>
       <c r="AF20">
         <v>9</v>
       </c>
       <c r="AG20">
-        <v>0.215</v>
+        <v>0.2434</v>
       </c>
       <c r="AH20">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI20">
-        <v>0.97909999999999997</v>
+        <v>0.9967</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -2988,16 +2959,16 @@
         <v>84</v>
       </c>
       <c r="C21">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D21">
-        <v>129</v>
+        <v>-132</v>
       </c>
       <c r="E21">
-        <v>-140</v>
-      </c>
-      <c r="F21" s="2">
-        <v>6.0665901977500374</v>
+        <v>113</v>
+      </c>
+      <c r="F21">
+        <v>4.28</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -3006,22 +2977,22 @@
         <v>45</v>
       </c>
       <c r="K21">
-        <v>6.03</v>
+        <v>4.28</v>
       </c>
       <c r="L21" t="s">
         <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N21">
-        <v>824883</v>
+        <v>823511</v>
       </c>
       <c r="O21" t="s">
         <v>48</v>
       </c>
       <c r="P21">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -3030,87 +3001,87 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>0.22950000000000001</v>
+        <v>0.2298</v>
       </c>
       <c r="U21">
-        <v>0.23480000000000001</v>
+        <v>0.2243</v>
       </c>
       <c r="V21">
         <v>5</v>
       </c>
       <c r="W21">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="X21">
-        <v>0.2437</v>
+        <v>0.2136</v>
       </c>
       <c r="Y21">
-        <v>0.373</v>
+        <v>0.34</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>4.24</v>
+        <v>4.35</v>
       </c>
       <c r="AB21">
-        <v>1.1464000000000001</v>
+        <v>0.8611</v>
       </c>
       <c r="AC21" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD21">
-        <v>0.2525</v>
+        <v>0.1944</v>
       </c>
       <c r="AE21">
-        <v>0.25080000000000002</v>
+        <v>0.1849</v>
       </c>
       <c r="AF21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG21">
-        <v>0.2243</v>
+        <v>0.2261</v>
       </c>
       <c r="AH21">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI21">
-        <v>0.99750000000000005</v>
+        <v>0.9889</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
       </c>
       <c r="AK21" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C22">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D22">
-        <v>-111</v>
+        <v>110</v>
       </c>
       <c r="E22">
-        <v>-107</v>
-      </c>
-      <c r="F22" s="2">
-        <v>5.0908962815780567</v>
+        <v>-125</v>
+      </c>
+      <c r="F22">
+        <v>4.65</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -3119,22 +3090,22 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>4.9000000000000004</v>
+        <v>4.65</v>
       </c>
       <c r="L22" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N22">
-        <v>824562</v>
+        <v>822779</v>
       </c>
       <c r="O22" t="s">
         <v>48</v>
       </c>
       <c r="P22">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -3143,87 +3114,78 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>0.19739999999999999</v>
+        <v>0.2547</v>
       </c>
       <c r="U22">
-        <v>0.17849999999999999</v>
+        <v>0.2611</v>
       </c>
       <c r="V22">
         <v>5</v>
       </c>
       <c r="W22">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="X22">
-        <v>0.14749999999999999</v>
+        <v>0.2759</v>
       </c>
       <c r="Y22">
-        <v>0.379</v>
+        <v>0.303</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>4.45</v>
+        <v>4.12</v>
       </c>
       <c r="AB22">
-        <v>1.143</v>
+        <v>0.8571</v>
       </c>
       <c r="AC22" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD22">
-        <v>0.25180000000000002</v>
+        <v>0.1934</v>
       </c>
       <c r="AE22">
-        <v>0.26750000000000002</v>
+        <v>0.1835</v>
       </c>
       <c r="AF22">
         <v>9</v>
       </c>
       <c r="AG22">
-        <v>0.2555</v>
+        <v>0.215</v>
       </c>
       <c r="AH22">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI22">
-        <v>1.0521</v>
+        <v>0.9791</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL22" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C23">
-        <v>4.5</v>
-      </c>
-      <c r="D23">
-        <v>134</v>
-      </c>
-      <c r="E23">
-        <v>-155</v>
-      </c>
-      <c r="F23" s="2">
-        <v>4.4071276909766404</v>
+        <v>87</v>
+      </c>
+      <c r="F23">
+        <v>4.07</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -3232,22 +3194,22 @@
         <v>45</v>
       </c>
       <c r="K23">
-        <v>4.26</v>
+        <v>4.07</v>
       </c>
       <c r="L23" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="N23">
-        <v>824562</v>
+        <v>822779</v>
       </c>
       <c r="O23" t="s">
         <v>48</v>
       </c>
       <c r="P23">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -3256,87 +3218,78 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>0.1825</v>
+        <v>0.2448</v>
       </c>
       <c r="U23">
-        <v>0.1893</v>
+        <v>0.2207</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X23">
-        <v>0.20180000000000001</v>
+        <v>0.1759</v>
       </c>
       <c r="Y23">
-        <v>0.35299999999999998</v>
+        <v>0.351</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>4.49</v>
+        <v>4.16</v>
       </c>
       <c r="AB23">
-        <v>1.0101</v>
+        <v>0.8303</v>
       </c>
       <c r="AC23" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD23">
-        <v>0.2225</v>
+        <v>0.1874</v>
       </c>
       <c r="AE23">
-        <v>0.24249999999999999</v>
+        <v>0.1897</v>
       </c>
       <c r="AF23">
         <v>9</v>
       </c>
       <c r="AG23">
-        <v>0.23710000000000001</v>
+        <v>0.2181</v>
       </c>
       <c r="AH23">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI23">
-        <v>1.0266999999999999</v>
+        <v>0.9631</v>
       </c>
       <c r="AJ23" t="b">
         <v>1</v>
       </c>
       <c r="AK23" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL23" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24">
-        <v>4.5</v>
-      </c>
-      <c r="D24">
-        <v>131</v>
-      </c>
-      <c r="E24">
-        <v>-166</v>
-      </c>
-      <c r="F24" s="2">
-        <v>2.8748358220486776</v>
+        <v>88</v>
+      </c>
+      <c r="F24">
+        <v>3.75</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3345,22 +3298,22 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>2.73</v>
+        <v>3.75</v>
       </c>
       <c r="L24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N24">
-        <v>823916</v>
+        <v>824883</v>
       </c>
       <c r="O24" t="s">
         <v>48</v>
       </c>
       <c r="P24">
-        <v>5.0999999999999996</v>
+        <v>5.6</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -3369,87 +3322,87 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>0.14649999999999999</v>
+        <v>0.1765</v>
       </c>
       <c r="U24">
-        <v>0.13930000000000001</v>
+        <v>0.1681</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
       <c r="W24">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="X24">
-        <v>0.12709999999999999</v>
+        <v>0.1532</v>
       </c>
       <c r="Y24">
-        <v>0.371</v>
+        <v>0.357</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>4.2300000000000004</v>
+        <v>3.89</v>
       </c>
       <c r="AB24">
-        <v>0.94820000000000004</v>
+        <v>1.0049</v>
       </c>
       <c r="AC24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD24">
-        <v>0.2089</v>
+        <v>0.2268</v>
       </c>
       <c r="AE24">
-        <v>0.21240000000000001</v>
+        <v>0.2191</v>
       </c>
       <c r="AF24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG24">
-        <v>0.2142</v>
+        <v>0.2094</v>
       </c>
       <c r="AH24">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI24">
-        <v>0.96530000000000005</v>
+        <v>1.016</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL24" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C25">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="E25">
-        <v>-119</v>
-      </c>
-      <c r="F25" s="2">
-        <v>3.7774306226209875</v>
+        <v>-140</v>
+      </c>
+      <c r="F25">
+        <v>5.89</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3458,22 +3411,22 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>3.74</v>
+        <v>5.89</v>
       </c>
       <c r="L25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="N25">
-        <v>823994</v>
+        <v>824883</v>
       </c>
       <c r="O25" t="s">
         <v>48</v>
       </c>
       <c r="P25">
-        <v>4.5999999999999996</v>
+        <v>5.3</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3482,87 +3435,87 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>0.15579999999999999</v>
+        <v>0.2295</v>
       </c>
       <c r="U25">
-        <v>0.15540000000000001</v>
+        <v>0.2348</v>
       </c>
       <c r="V25">
         <v>5</v>
       </c>
       <c r="W25">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="X25">
-        <v>0.1545</v>
+        <v>0.2437</v>
       </c>
       <c r="Y25">
-        <v>0.35499999999999998</v>
+        <v>0.373</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="AB25">
-        <v>1.2202999999999999</v>
+        <v>1.1189</v>
       </c>
       <c r="AC25" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD25">
-        <v>0.26879999999999998</v>
+        <v>0.2525</v>
       </c>
       <c r="AE25">
-        <v>0.26400000000000001</v>
+        <v>0.2508</v>
       </c>
       <c r="AF25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG25">
-        <v>0.25080000000000002</v>
+        <v>0.2243</v>
       </c>
       <c r="AH25">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI25">
-        <v>1.0161</v>
+        <v>0.9975</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL25" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C26">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E26">
-        <v>-149</v>
-      </c>
-      <c r="F26" s="2">
-        <v>4.2632427752087452</v>
+        <v>-155</v>
+      </c>
+      <c r="F26">
+        <v>4.15</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3571,22 +3524,22 @@
         <v>45</v>
       </c>
       <c r="K26">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="L26" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="N26">
-        <v>822779</v>
+        <v>824562</v>
       </c>
       <c r="O26" t="s">
         <v>48</v>
       </c>
       <c r="P26">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -3595,87 +3548,87 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>0.24479999999999999</v>
+        <v>0.1825</v>
       </c>
       <c r="U26">
-        <v>0.22070000000000001</v>
+        <v>0.1893</v>
       </c>
       <c r="V26">
         <v>5</v>
       </c>
       <c r="W26">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X26">
-        <v>0.1759</v>
+        <v>0.2018</v>
       </c>
       <c r="Y26">
-        <v>0.35099999999999998</v>
+        <v>0.353</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>4.16</v>
+        <v>4.49</v>
       </c>
       <c r="AB26">
-        <v>0.85070000000000001</v>
+        <v>0.9859</v>
       </c>
       <c r="AC26" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD26">
-        <v>0.18740000000000001</v>
+        <v>0.2225</v>
       </c>
       <c r="AE26">
-        <v>0.18970000000000001</v>
+        <v>0.2425</v>
       </c>
       <c r="AF26">
         <v>9</v>
       </c>
       <c r="AG26">
-        <v>0.21809999999999999</v>
+        <v>0.2371</v>
       </c>
       <c r="AH26">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI26">
-        <v>0.96309999999999996</v>
+        <v>1.0267</v>
       </c>
       <c r="AJ26" t="b">
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL26" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C27">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D27">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="E27">
-        <v>102</v>
-      </c>
-      <c r="F27" s="2">
-        <v>3.8800218899146075</v>
+        <v>-107</v>
+      </c>
+      <c r="F27">
+        <v>4.78</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3684,22 +3637,22 @@
         <v>45</v>
       </c>
       <c r="K27">
-        <v>3.84</v>
+        <v>4.78</v>
       </c>
       <c r="L27" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N27">
-        <v>824883</v>
+        <v>824562</v>
       </c>
       <c r="O27" t="s">
         <v>48</v>
       </c>
       <c r="P27">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -3708,71 +3661,551 @@
         <v>0</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>0.17649999999999999</v>
+        <v>0.1974</v>
       </c>
       <c r="U27">
-        <v>0.1681</v>
+        <v>0.1785</v>
       </c>
       <c r="V27">
         <v>5</v>
       </c>
       <c r="W27">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="X27">
-        <v>0.1532</v>
+        <v>0.1475</v>
       </c>
       <c r="Y27">
-        <v>0.35699999999999998</v>
+        <v>0.379</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>3.89</v>
+        <v>4.45</v>
       </c>
       <c r="AB27">
-        <v>1.0296000000000001</v>
+        <v>1.1157</v>
       </c>
       <c r="AC27" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="AD27">
-        <v>0.2268</v>
+        <v>0.2518</v>
       </c>
       <c r="AE27">
-        <v>0.21909999999999999</v>
+        <v>0.2675</v>
       </c>
       <c r="AF27">
         <v>9</v>
       </c>
       <c r="AG27">
-        <v>0.2094</v>
+        <v>0.2555</v>
       </c>
       <c r="AH27">
-        <v>0.2203</v>
+        <v>0.2257</v>
       </c>
       <c r="AI27">
-        <v>1.016</v>
+        <v>1.0521</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL27" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM27">
         <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28">
+        <v>1.63</v>
+      </c>
+      <c r="H28" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28">
+        <v>1.63</v>
+      </c>
+      <c r="L28" t="s">
+        <v>46</v>
+      </c>
+      <c r="M28" t="s">
+        <v>95</v>
+      </c>
+      <c r="N28">
+        <v>823916</v>
+      </c>
+      <c r="O28" t="s">
+        <v>96</v>
+      </c>
+      <c r="P28">
+        <v>1.7</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0.1917</v>
+      </c>
+      <c r="U28">
+        <v>0.1921</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>10</v>
+      </c>
+      <c r="X28">
+        <v>0.2</v>
+      </c>
+      <c r="Y28">
+        <v>0.048</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>4.05</v>
+      </c>
+      <c r="AB28">
+        <v>1.2477</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD28">
+        <v>0.2816</v>
+      </c>
+      <c r="AE28">
+        <v>0.2198</v>
+      </c>
+      <c r="AF28">
+        <v>9</v>
+      </c>
+      <c r="AG28">
+        <v>0.1984</v>
+      </c>
+      <c r="AH28">
+        <v>0.2257</v>
+      </c>
+      <c r="AI28">
+        <v>1.0072</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29">
+        <v>4.5</v>
+      </c>
+      <c r="D29">
+        <v>131</v>
+      </c>
+      <c r="E29">
+        <v>-166</v>
+      </c>
+      <c r="F29">
+        <v>2.67</v>
+      </c>
+      <c r="H29" t="s">
+        <v>45</v>
+      </c>
+      <c r="J29" t="s">
+        <v>45</v>
+      </c>
+      <c r="K29">
+        <v>2.67</v>
+      </c>
+      <c r="L29" t="s">
+        <v>46</v>
+      </c>
+      <c r="M29" t="s">
+        <v>95</v>
+      </c>
+      <c r="N29">
+        <v>823916</v>
+      </c>
+      <c r="O29" t="s">
+        <v>48</v>
+      </c>
+      <c r="P29">
+        <v>5.1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>6</v>
+      </c>
+      <c r="T29">
+        <v>0.1465</v>
+      </c>
+      <c r="U29">
+        <v>0.1393</v>
+      </c>
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
+        <v>118</v>
+      </c>
+      <c r="X29">
+        <v>0.1271</v>
+      </c>
+      <c r="Y29">
+        <v>0.371</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>4.23</v>
+      </c>
+      <c r="AB29">
+        <v>0.9255</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD29">
+        <v>0.2089</v>
+      </c>
+      <c r="AE29">
+        <v>0.2124</v>
+      </c>
+      <c r="AF29">
+        <v>8</v>
+      </c>
+      <c r="AG29">
+        <v>0.2142</v>
+      </c>
+      <c r="AH29">
+        <v>0.2257</v>
+      </c>
+      <c r="AI29">
+        <v>0.9653</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30">
+        <v>3.5</v>
+      </c>
+      <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
+        <v>-119</v>
+      </c>
+      <c r="F30">
+        <v>3.65</v>
+      </c>
+      <c r="H30" t="s">
+        <v>45</v>
+      </c>
+      <c r="J30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K30">
+        <v>3.65</v>
+      </c>
+      <c r="L30" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" t="s">
+        <v>99</v>
+      </c>
+      <c r="N30">
+        <v>823994</v>
+      </c>
+      <c r="O30" t="s">
+        <v>48</v>
+      </c>
+      <c r="P30">
+        <v>4.6</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>6</v>
+      </c>
+      <c r="T30">
+        <v>0.1558</v>
+      </c>
+      <c r="U30">
+        <v>0.1554</v>
+      </c>
+      <c r="V30">
+        <v>5</v>
+      </c>
+      <c r="W30">
+        <v>110</v>
+      </c>
+      <c r="X30">
+        <v>0.1545</v>
+      </c>
+      <c r="Y30">
+        <v>0.355</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>4.2</v>
+      </c>
+      <c r="AB30">
+        <v>1.1911</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD30">
+        <v>0.2688</v>
+      </c>
+      <c r="AE30">
+        <v>0.264</v>
+      </c>
+      <c r="AF30">
+        <v>9</v>
+      </c>
+      <c r="AG30">
+        <v>0.2508</v>
+      </c>
+      <c r="AH30">
+        <v>0.2257</v>
+      </c>
+      <c r="AI30">
+        <v>1.0161</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <v>5.5</v>
+      </c>
+      <c r="D31">
+        <v>128</v>
+      </c>
+      <c r="E31">
+        <v>-149</v>
+      </c>
+      <c r="H31" t="s">
+        <v>45</v>
+      </c>
+      <c r="J31" t="s">
+        <v>45</v>
+      </c>
+      <c r="L31" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" t="s">
+        <v>86</v>
+      </c>
+      <c r="N31" t="s">
+        <v>45</v>
+      </c>
+      <c r="O31" t="s">
+        <v>45</v>
+      </c>
+      <c r="S31">
+        <v>6</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32">
+        <v>3.5</v>
+      </c>
+      <c r="D32">
+        <v>-109</v>
+      </c>
+      <c r="E32">
+        <v>102</v>
+      </c>
+      <c r="H32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
+      <c r="L32" t="s">
+        <v>45</v>
+      </c>
+      <c r="M32" t="s">
+        <v>89</v>
+      </c>
+      <c r="N32" t="s">
+        <v>45</v>
+      </c>
+      <c r="O32" t="s">
+        <v>45</v>
+      </c>
+      <c r="S32">
+        <v>6</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33">
+        <v>4.5</v>
+      </c>
+      <c r="D33">
+        <v>-109</v>
+      </c>
+      <c r="E33">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>45</v>
+      </c>
+      <c r="J33" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" t="s">
+        <v>99</v>
+      </c>
+      <c r="N33" t="s">
+        <v>45</v>
+      </c>
+      <c r="O33" t="s">
+        <v>45</v>
+      </c>
+      <c r="S33">
+        <v>6</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/k-props/2026-08-12.xlsx
+++ b/data/k-props/2026-08-12.xlsx
@@ -854,7 +854,7 @@
         <v>101</v>
       </c>
       <c r="F2">
-        <v>4.49</v>
+        <v>4.12</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -863,7 +863,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>4.49</v>
+        <v>4.12</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -878,7 +878,7 @@
         <v>48</v>
       </c>
       <c r="P2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -890,31 +890,31 @@
         <v>4</v>
       </c>
       <c r="T2">
-        <v>0.2069</v>
+        <v>0.204</v>
       </c>
       <c r="U2">
-        <v>0.2238</v>
+        <v>0.1994</v>
       </c>
       <c r="V2">
         <v>5</v>
       </c>
       <c r="W2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="X2">
-        <v>0.2521</v>
+        <v>0.1913</v>
       </c>
       <c r="Y2">
-        <v>0.373</v>
+        <v>0.365</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="AB2">
-        <v>0.8726</v>
+        <v>0.8712</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -932,7 +932,7 @@
         <v>0.2101</v>
       </c>
       <c r="AH2">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI2">
         <v>0.9518</v>
@@ -967,7 +967,7 @@
         <v>-129</v>
       </c>
       <c r="F3">
-        <v>6.17</v>
+        <v>6.3</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -976,7 +976,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>6.17</v>
+        <v>6.3</v>
       </c>
       <c r="L3" t="s">
         <v>52</v>
@@ -991,7 +991,7 @@
         <v>48</v>
       </c>
       <c r="P3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -1003,31 +1003,31 @@
         <v>4</v>
       </c>
       <c r="T3">
-        <v>0.2027</v>
+        <v>0.2021</v>
       </c>
       <c r="U3">
-        <v>0.2086</v>
+        <v>0.2073</v>
       </c>
       <c r="V3">
         <v>5</v>
       </c>
       <c r="W3">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="X3">
-        <v>0.2211</v>
+        <v>0.217</v>
       </c>
       <c r="Y3">
-        <v>0.322</v>
+        <v>0.346</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.25</v>
+        <v>4.28</v>
       </c>
       <c r="AB3">
-        <v>1.1957</v>
+        <v>1.1938</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -1045,7 +1045,7 @@
         <v>0.2379</v>
       </c>
       <c r="AH3">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI3">
         <v>1.0698</v>
@@ -1080,7 +1080,7 @@
         <v>134</v>
       </c>
       <c r="F4">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1089,10 +1089,10 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M4" t="s">
         <v>54</v>
@@ -1104,7 +1104,7 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1116,22 +1116,22 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>0.3063</v>
+        <v>0.3098</v>
       </c>
       <c r="U4">
-        <v>0.3196</v>
+        <v>0.3168</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="X4">
-        <v>0.3469</v>
+        <v>0.3333</v>
       </c>
       <c r="Y4">
-        <v>0.329</v>
+        <v>0.296</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>3.91</v>
       </c>
       <c r="AB4">
-        <v>0.8957</v>
+        <v>0.8943</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1158,7 +1158,7 @@
         <v>0.2126</v>
       </c>
       <c r="AH4">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI4">
         <v>0.9321</v>
@@ -1193,7 +1193,7 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1202,7 +1202,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
@@ -1217,7 +1217,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1229,31 +1229,31 @@
         <v>6</v>
       </c>
       <c r="T5">
-        <v>0.2071</v>
+        <v>0.2106</v>
       </c>
       <c r="U5">
-        <v>0.2247</v>
+        <v>0.2312</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X5">
-        <v>0.26</v>
+        <v>0.2727</v>
       </c>
       <c r="Y5">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="AB5">
-        <v>0.8038</v>
+        <v>0.8025</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1268,10 +1268,10 @@
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>0.2259</v>
+        <v>0.2264</v>
       </c>
       <c r="AH5">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI5">
         <v>0.944</v>
@@ -1306,7 +1306,7 @@
         <v>115</v>
       </c>
       <c r="F6">
-        <v>7.69</v>
+        <v>7.68</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1315,7 +1315,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>8.27</v>
+        <v>8.26</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -1366,7 +1366,7 @@
         <v>3.9</v>
       </c>
       <c r="AB6">
-        <v>1.2123</v>
+        <v>1.2103</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1384,7 +1384,7 @@
         <v>0.2171</v>
       </c>
       <c r="AH6">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI6">
         <v>1.0849</v>
@@ -1479,7 +1479,7 @@
         <v>4.55</v>
       </c>
       <c r="AB7">
-        <v>0.9162</v>
+        <v>0.9148</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1497,7 +1497,7 @@
         <v>0.192</v>
       </c>
       <c r="AH7">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI7">
         <v>0.88</v>
@@ -1592,7 +1592,7 @@
         <v>4.37</v>
       </c>
       <c r="AB8">
-        <v>0.852</v>
+        <v>0.8507</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1610,7 +1610,7 @@
         <v>0.2002</v>
       </c>
       <c r="AH8">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI8">
         <v>0.88</v>
@@ -1645,7 +1645,7 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1654,7 +1654,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
@@ -1705,7 +1705,7 @@
         <v>4.33</v>
       </c>
       <c r="AB9">
-        <v>1.2292</v>
+        <v>1.2272</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1723,7 +1723,7 @@
         <v>0.2166</v>
       </c>
       <c r="AH9">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI9">
         <v>1.0549</v>
@@ -1794,7 +1794,7 @@
         <v>4.38</v>
       </c>
       <c r="AB10">
-        <v>1.2097</v>
+        <v>1.2078</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
@@ -1812,7 +1812,7 @@
         <v>0.2341</v>
       </c>
       <c r="AH10">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI10">
         <v>1.0778</v>
@@ -1838,7 +1838,7 @@
         <v>66</v>
       </c>
       <c r="F11">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1847,7 +1847,7 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
@@ -1898,7 +1898,7 @@
         <v>4.19</v>
       </c>
       <c r="AB11">
-        <v>1.2097</v>
+        <v>1.2078</v>
       </c>
       <c r="AC11" t="s">
         <v>49</v>
@@ -1916,7 +1916,7 @@
         <v>0.2015</v>
       </c>
       <c r="AH11">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI11">
         <v>0.9583</v>
@@ -2011,7 +2011,7 @@
         <v>4.37</v>
       </c>
       <c r="AB12">
-        <v>0.8538</v>
+        <v>0.8524</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
@@ -2029,7 +2029,7 @@
         <v>0.2163</v>
       </c>
       <c r="AH12">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI12">
         <v>0.8914</v>
@@ -2124,7 +2124,7 @@
         <v>4.19</v>
       </c>
       <c r="AB13">
-        <v>0.7222</v>
+        <v>0.7211</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
@@ -2142,7 +2142,7 @@
         <v>0.2193</v>
       </c>
       <c r="AH13">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI13">
         <v>0.9807</v>
@@ -2177,7 +2177,7 @@
         <v>127</v>
       </c>
       <c r="F14">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2186,7 +2186,7 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
@@ -2237,7 +2237,7 @@
         <v>4.21</v>
       </c>
       <c r="AB14">
-        <v>1.049</v>
+        <v>1.0473</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
@@ -2255,7 +2255,7 @@
         <v>0.2157</v>
       </c>
       <c r="AH14">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI14">
         <v>0.9557</v>
@@ -2290,7 +2290,7 @@
         <v>-150</v>
       </c>
       <c r="F15">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2299,7 +2299,7 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
@@ -2350,7 +2350,7 @@
         <v>4.09</v>
       </c>
       <c r="AB15">
-        <v>0.8799</v>
+        <v>0.8785</v>
       </c>
       <c r="AC15" t="s">
         <v>74</v>
@@ -2368,7 +2368,7 @@
         <v>0.2263</v>
       </c>
       <c r="AH15">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI15">
         <v>0.9855</v>
@@ -2403,7 +2403,7 @@
         <v>-122</v>
       </c>
       <c r="F16">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2412,7 +2412,7 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
@@ -2463,7 +2463,7 @@
         <v>4.38</v>
       </c>
       <c r="AB16">
-        <v>0.9597</v>
+        <v>0.9582</v>
       </c>
       <c r="AC16" t="s">
         <v>74</v>
@@ -2481,7 +2481,7 @@
         <v>0.2295</v>
       </c>
       <c r="AH16">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI16">
         <v>0.9526</v>
@@ -2516,7 +2516,7 @@
         <v>-106</v>
       </c>
       <c r="F17">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2525,7 +2525,7 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
@@ -2576,16 +2576,16 @@
         <v>4.29</v>
       </c>
       <c r="AB17">
-        <v>1.1019</v>
+        <v>1.1477</v>
       </c>
       <c r="AC17" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD17">
-        <v>0.2487</v>
+        <v>0.2594</v>
       </c>
       <c r="AE17">
-        <v>0.2443</v>
+        <v>0.2517</v>
       </c>
       <c r="AF17">
         <v>9</v>
@@ -2594,19 +2594,19 @@
         <v>0.2104</v>
       </c>
       <c r="AH17">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI17">
-        <v>0.9888</v>
+        <v>0.9334</v>
       </c>
       <c r="AJ17" t="b">
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL17" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2629,7 +2629,7 @@
         <v>-150</v>
       </c>
       <c r="F18">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2638,7 +2638,7 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="L18" t="s">
         <v>46</v>
@@ -2689,7 +2689,7 @@
         <v>4.29</v>
       </c>
       <c r="AB18">
-        <v>0.9953</v>
+        <v>0.9937</v>
       </c>
       <c r="AC18" t="s">
         <v>74</v>
@@ -2707,7 +2707,7 @@
         <v>0.2367</v>
       </c>
       <c r="AH18">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI18">
         <v>1.01</v>
@@ -2802,7 +2802,7 @@
         <v>4.49</v>
       </c>
       <c r="AB19">
-        <v>0.9286</v>
+        <v>0.9271</v>
       </c>
       <c r="AC19" t="s">
         <v>74</v>
@@ -2820,7 +2820,7 @@
         <v>0.2351</v>
       </c>
       <c r="AH19">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI19">
         <v>1.0033</v>
@@ -2855,7 +2855,7 @@
         <v>-115</v>
       </c>
       <c r="F20">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2864,7 +2864,7 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
@@ -2915,7 +2915,7 @@
         <v>3.87</v>
       </c>
       <c r="AB20">
-        <v>1.2176</v>
+        <v>1.2157</v>
       </c>
       <c r="AC20" t="s">
         <v>74</v>
@@ -2933,7 +2933,7 @@
         <v>0.2434</v>
       </c>
       <c r="AH20">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI20">
         <v>0.9967</v>
@@ -2968,7 +2968,7 @@
         <v>113</v>
       </c>
       <c r="F21">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2977,7 +2977,7 @@
         <v>45</v>
       </c>
       <c r="K21">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="L21" t="s">
         <v>46</v>
@@ -3028,7 +3028,7 @@
         <v>4.35</v>
       </c>
       <c r="AB21">
-        <v>0.8611</v>
+        <v>0.8597</v>
       </c>
       <c r="AC21" t="s">
         <v>74</v>
@@ -3046,7 +3046,7 @@
         <v>0.2261</v>
       </c>
       <c r="AH21">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI21">
         <v>0.9889</v>
@@ -3081,7 +3081,7 @@
         <v>-125</v>
       </c>
       <c r="F22">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -3090,7 +3090,7 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
@@ -3141,7 +3141,7 @@
         <v>4.12</v>
       </c>
       <c r="AB22">
-        <v>0.8571</v>
+        <v>0.8557</v>
       </c>
       <c r="AC22" t="s">
         <v>74</v>
@@ -3159,7 +3159,7 @@
         <v>0.215</v>
       </c>
       <c r="AH22">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI22">
         <v>0.9791</v>
@@ -3245,7 +3245,7 @@
         <v>4.16</v>
       </c>
       <c r="AB23">
-        <v>0.8303</v>
+        <v>0.829</v>
       </c>
       <c r="AC23" t="s">
         <v>74</v>
@@ -3263,7 +3263,7 @@
         <v>0.2181</v>
       </c>
       <c r="AH23">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI23">
         <v>0.9631</v>
@@ -3349,7 +3349,7 @@
         <v>3.89</v>
       </c>
       <c r="AB24">
-        <v>1.0049</v>
+        <v>1.0033</v>
       </c>
       <c r="AC24" t="s">
         <v>74</v>
@@ -3367,7 +3367,7 @@
         <v>0.2094</v>
       </c>
       <c r="AH24">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI24">
         <v>1.016</v>
@@ -3402,7 +3402,7 @@
         <v>-140</v>
       </c>
       <c r="F25">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3411,7 +3411,7 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
@@ -3462,7 +3462,7 @@
         <v>4.24</v>
       </c>
       <c r="AB25">
-        <v>1.1189</v>
+        <v>1.1171</v>
       </c>
       <c r="AC25" t="s">
         <v>74</v>
@@ -3480,7 +3480,7 @@
         <v>0.2243</v>
       </c>
       <c r="AH25">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI25">
         <v>0.9975</v>
@@ -3575,7 +3575,7 @@
         <v>4.49</v>
       </c>
       <c r="AB26">
-        <v>0.9859</v>
+        <v>0.9843</v>
       </c>
       <c r="AC26" t="s">
         <v>74</v>
@@ -3593,7 +3593,7 @@
         <v>0.2371</v>
       </c>
       <c r="AH26">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI26">
         <v>1.0267</v>
@@ -3628,7 +3628,7 @@
         <v>-107</v>
       </c>
       <c r="F27">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3637,7 +3637,7 @@
         <v>45</v>
       </c>
       <c r="K27">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
@@ -3688,7 +3688,7 @@
         <v>4.45</v>
       </c>
       <c r="AB27">
-        <v>1.1157</v>
+        <v>1.1139</v>
       </c>
       <c r="AC27" t="s">
         <v>74</v>
@@ -3706,7 +3706,7 @@
         <v>0.2555</v>
       </c>
       <c r="AH27">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI27">
         <v>1.0521</v>
@@ -3792,7 +3792,7 @@
         <v>4.05</v>
       </c>
       <c r="AB28">
-        <v>1.2477</v>
+        <v>1.2457</v>
       </c>
       <c r="AC28" t="s">
         <v>74</v>
@@ -3810,7 +3810,7 @@
         <v>0.1984</v>
       </c>
       <c r="AH28">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI28">
         <v>1.0072</v>
@@ -3845,7 +3845,7 @@
         <v>-166</v>
       </c>
       <c r="F29">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3854,7 +3854,7 @@
         <v>45</v>
       </c>
       <c r="K29">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="L29" t="s">
         <v>46</v>
@@ -3905,7 +3905,7 @@
         <v>4.23</v>
       </c>
       <c r="AB29">
-        <v>0.9255</v>
+        <v>0.924</v>
       </c>
       <c r="AC29" t="s">
         <v>74</v>
@@ -3923,7 +3923,7 @@
         <v>0.2142</v>
       </c>
       <c r="AH29">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI29">
         <v>0.9653</v>
@@ -3958,7 +3958,7 @@
         <v>-119</v>
       </c>
       <c r="F30">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="H30" t="s">
         <v>45</v>
@@ -3967,7 +3967,7 @@
         <v>45</v>
       </c>
       <c r="K30">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="L30" t="s">
         <v>46</v>
@@ -4018,7 +4018,7 @@
         <v>4.2</v>
       </c>
       <c r="AB30">
-        <v>1.1911</v>
+        <v>1.1892</v>
       </c>
       <c r="AC30" t="s">
         <v>74</v>
@@ -4036,7 +4036,7 @@
         <v>0.2508</v>
       </c>
       <c r="AH30">
-        <v>0.2257</v>
+        <v>0.2261</v>
       </c>
       <c r="AI30">
         <v>1.0161</v>

--- a/data/k-props/2026-08-12.xlsx
+++ b/data/k-props/2026-08-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="104">
   <si>
     <t>date</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
   </si>
   <si>
     <t>Ryan Feltner</t>
@@ -854,7 +857,7 @@
         <v>101</v>
       </c>
       <c r="F2">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -863,7 +866,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -893,19 +896,19 @@
         <v>0.204</v>
       </c>
       <c r="U2">
-        <v>0.1994</v>
+        <v>0.2019</v>
       </c>
       <c r="V2">
         <v>5</v>
       </c>
       <c r="W2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X2">
-        <v>0.1913</v>
+        <v>0.1983</v>
       </c>
       <c r="Y2">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -914,7 +917,7 @@
         <v>4.29</v>
       </c>
       <c r="AB2">
-        <v>0.8712</v>
+        <v>0.8743</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -932,7 +935,7 @@
         <v>0.2101</v>
       </c>
       <c r="AH2">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI2">
         <v>0.9518</v>
@@ -967,7 +970,7 @@
         <v>-129</v>
       </c>
       <c r="F3">
-        <v>6.3</v>
+        <v>6.24</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -976,7 +979,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>6.3</v>
+        <v>6.24</v>
       </c>
       <c r="L3" t="s">
         <v>52</v>
@@ -991,7 +994,7 @@
         <v>48</v>
       </c>
       <c r="P3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -1003,31 +1006,31 @@
         <v>4</v>
       </c>
       <c r="T3">
-        <v>0.2021</v>
+        <v>0.199</v>
       </c>
       <c r="U3">
-        <v>0.2073</v>
+        <v>0.2013</v>
       </c>
       <c r="V3">
         <v>5</v>
       </c>
       <c r="W3">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="X3">
-        <v>0.217</v>
+        <v>0.2054</v>
       </c>
       <c r="Y3">
-        <v>0.346</v>
+        <v>0.359</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="AB3">
-        <v>1.1938</v>
+        <v>1.1981</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -1045,7 +1048,7 @@
         <v>0.2379</v>
       </c>
       <c r="AH3">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI3">
         <v>1.0698</v>
@@ -1080,7 +1083,7 @@
         <v>134</v>
       </c>
       <c r="F4">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1089,7 +1092,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="L4" t="s">
         <v>46</v>
@@ -1104,7 +1107,7 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1116,22 +1119,22 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>0.3098</v>
+        <v>0.3036</v>
       </c>
       <c r="U4">
-        <v>0.3168</v>
+        <v>0.3038</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="X4">
-        <v>0.3333</v>
+        <v>0.3043</v>
       </c>
       <c r="Y4">
-        <v>0.296</v>
+        <v>0.315</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1140,7 +1143,7 @@
         <v>3.91</v>
       </c>
       <c r="AB4">
-        <v>0.8943</v>
+        <v>0.8975</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1158,7 +1161,7 @@
         <v>0.2126</v>
       </c>
       <c r="AH4">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI4">
         <v>0.9321</v>
@@ -1193,7 +1196,7 @@
         <v>128</v>
       </c>
       <c r="F5">
-        <v>3.72</v>
+        <v>3.83</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1202,7 +1205,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>3.72</v>
+        <v>3.83</v>
       </c>
       <c r="L5" t="s">
         <v>46</v>
@@ -1217,7 +1220,7 @@
         <v>48</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1229,22 +1232,22 @@
         <v>6</v>
       </c>
       <c r="T5">
-        <v>0.2106</v>
+        <v>0.2108</v>
       </c>
       <c r="U5">
-        <v>0.2312</v>
+        <v>0.2328</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="X5">
         <v>0.2727</v>
       </c>
       <c r="Y5">
-        <v>0.331</v>
+        <v>0.355</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1253,7 +1256,7 @@
         <v>4.24</v>
       </c>
       <c r="AB5">
-        <v>0.8025</v>
+        <v>0.8055</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1271,7 +1274,7 @@
         <v>0.2264</v>
       </c>
       <c r="AH5">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI5">
         <v>0.944</v>
@@ -1306,7 +1309,7 @@
         <v>115</v>
       </c>
       <c r="F6">
-        <v>7.68</v>
+        <v>7.59</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1315,7 +1318,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>8.26</v>
+        <v>8.17</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -1330,7 +1333,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1342,22 +1345,22 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>0.268</v>
+        <v>0.2679</v>
       </c>
       <c r="U6">
-        <v>0.2854</v>
+        <v>0.2915</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="X6">
-        <v>0.3178</v>
+        <v>0.3402</v>
       </c>
       <c r="Y6">
-        <v>0.349</v>
+        <v>0.327</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1366,7 +1369,7 @@
         <v>3.9</v>
       </c>
       <c r="AB6">
-        <v>1.2103</v>
+        <v>1.2147</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1384,7 +1387,7 @@
         <v>0.2171</v>
       </c>
       <c r="AH6">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI6">
         <v>1.0849</v>
@@ -1419,7 +1422,7 @@
         <v>-147</v>
       </c>
       <c r="F7">
-        <v>4.39</v>
+        <v>3.82</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1428,7 +1431,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>4.39</v>
+        <v>3.82</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1440,10 +1443,10 @@
         <v>824967</v>
       </c>
       <c r="O7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="P7">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1455,31 +1458,31 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>0.2636</v>
+        <v>0.2556</v>
       </c>
       <c r="U7">
-        <v>0.2621</v>
+        <v>0.2419</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>0.2593</v>
+        <v>0.2128</v>
       </c>
       <c r="Y7">
-        <v>0.351</v>
+        <v>0.32</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="AB7">
-        <v>0.9148</v>
+        <v>0.9181</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1497,7 +1500,7 @@
         <v>0.192</v>
       </c>
       <c r="AH7">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI7">
         <v>0.88</v>
@@ -1520,7 +1523,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1532,7 +1535,7 @@
         <v>-156</v>
       </c>
       <c r="F8">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1541,13 +1544,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="L8" t="s">
         <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N8">
         <v>825047</v>
@@ -1592,7 +1595,7 @@
         <v>4.37</v>
       </c>
       <c r="AB8">
-        <v>0.8507</v>
+        <v>0.8538</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1610,7 +1613,7 @@
         <v>0.2002</v>
       </c>
       <c r="AH8">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI8">
         <v>0.88</v>
@@ -1633,7 +1636,7 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>4.5</v>
@@ -1645,7 +1648,7 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1654,13 +1657,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N9">
         <v>825047</v>
@@ -1705,7 +1708,7 @@
         <v>4.33</v>
       </c>
       <c r="AB9">
-        <v>1.2272</v>
+        <v>1.2317</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1723,7 +1726,7 @@
         <v>0.2166</v>
       </c>
       <c r="AH9">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI9">
         <v>1.0549</v>
@@ -1746,7 +1749,7 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10">
         <v>1.06</v>
@@ -1764,13 +1767,13 @@
         <v>46</v>
       </c>
       <c r="M10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N10">
         <v>823187</v>
       </c>
       <c r="O10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1794,7 +1797,7 @@
         <v>4.38</v>
       </c>
       <c r="AB10">
-        <v>1.2078</v>
+        <v>1.2122</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
@@ -1812,7 +1815,7 @@
         <v>0.2341</v>
       </c>
       <c r="AH10">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI10">
         <v>1.0778</v>
@@ -1835,10 +1838,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1847,19 +1850,19 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N11">
         <v>823187</v>
       </c>
       <c r="O11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P11">
         <v>4</v>
@@ -1898,7 +1901,7 @@
         <v>4.19</v>
       </c>
       <c r="AB11">
-        <v>1.2078</v>
+        <v>1.2122</v>
       </c>
       <c r="AC11" t="s">
         <v>49</v>
@@ -1916,7 +1919,7 @@
         <v>0.2015</v>
       </c>
       <c r="AH11">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI11">
         <v>0.9583</v>
@@ -1939,7 +1942,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <v>2.5</v>
@@ -1951,7 +1954,7 @@
         <v>140</v>
       </c>
       <c r="F12">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1960,13 +1963,13 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N12">
         <v>823187</v>
@@ -2011,7 +2014,7 @@
         <v>4.37</v>
       </c>
       <c r="AB12">
-        <v>0.8524</v>
+        <v>0.8555</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
@@ -2029,7 +2032,7 @@
         <v>0.2163</v>
       </c>
       <c r="AH12">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI12">
         <v>0.8914</v>
@@ -2052,7 +2055,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -2064,7 +2067,7 @@
         <v>110</v>
       </c>
       <c r="F13">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2073,13 +2076,13 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N13">
         <v>823263</v>
@@ -2124,7 +2127,7 @@
         <v>4.19</v>
       </c>
       <c r="AB13">
-        <v>0.7211</v>
+        <v>0.7237</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
@@ -2142,7 +2145,7 @@
         <v>0.2193</v>
       </c>
       <c r="AH13">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI13">
         <v>0.9807</v>
@@ -2165,7 +2168,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2177,7 +2180,7 @@
         <v>127</v>
       </c>
       <c r="F14">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2186,13 +2189,13 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N14">
         <v>823263</v>
@@ -2237,7 +2240,7 @@
         <v>4.21</v>
       </c>
       <c r="AB14">
-        <v>1.0473</v>
+        <v>1.0511</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
@@ -2255,7 +2258,7 @@
         <v>0.2157</v>
       </c>
       <c r="AH14">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI14">
         <v>0.9557</v>
@@ -2278,7 +2281,7 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2290,7 +2293,7 @@
         <v>-150</v>
       </c>
       <c r="F15">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2299,13 +2302,13 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N15">
         <v>824241</v>
@@ -2350,10 +2353,10 @@
         <v>4.09</v>
       </c>
       <c r="AB15">
-        <v>0.8785</v>
+        <v>0.8817</v>
       </c>
       <c r="AC15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD15">
         <v>0.1986</v>
@@ -2368,7 +2371,7 @@
         <v>0.2263</v>
       </c>
       <c r="AH15">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI15">
         <v>0.9855</v>
@@ -2377,10 +2380,10 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2391,7 +2394,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2403,7 +2406,7 @@
         <v>-122</v>
       </c>
       <c r="F16">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2412,13 +2415,13 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N16">
         <v>824241</v>
@@ -2463,16 +2466,16 @@
         <v>4.38</v>
       </c>
       <c r="AB16">
-        <v>0.9582</v>
+        <v>0.825</v>
       </c>
       <c r="AC16" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD16">
-        <v>0.2166</v>
+        <v>0.1858</v>
       </c>
       <c r="AE16">
-        <v>0.2066</v>
+        <v>0.1886</v>
       </c>
       <c r="AF16">
         <v>9</v>
@@ -2481,19 +2484,19 @@
         <v>0.2295</v>
       </c>
       <c r="AH16">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI16">
-        <v>0.9526</v>
+        <v>0.8885</v>
       </c>
       <c r="AJ16" t="b">
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL16" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM16">
         <v>0</v>
@@ -2504,7 +2507,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2516,7 +2519,7 @@
         <v>-106</v>
       </c>
       <c r="F17">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2525,13 +2528,13 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N17">
         <v>823833</v>
@@ -2576,7 +2579,7 @@
         <v>4.29</v>
       </c>
       <c r="AB17">
-        <v>1.1477</v>
+        <v>1.1519</v>
       </c>
       <c r="AC17" t="s">
         <v>49</v>
@@ -2594,7 +2597,7 @@
         <v>0.2104</v>
       </c>
       <c r="AH17">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI17">
         <v>0.9334</v>
@@ -2617,7 +2620,7 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2629,7 +2632,7 @@
         <v>-150</v>
       </c>
       <c r="F18">
-        <v>4.05</v>
+        <v>4.28</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2638,13 +2641,13 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>4.05</v>
+        <v>4.28</v>
       </c>
       <c r="L18" t="s">
         <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N18">
         <v>823833</v>
@@ -2689,37 +2692,37 @@
         <v>4.29</v>
       </c>
       <c r="AB18">
-        <v>0.9937</v>
+        <v>1.0365</v>
       </c>
       <c r="AC18" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD18">
-        <v>0.2246</v>
+        <v>0.2335</v>
       </c>
       <c r="AE18">
-        <v>0.2433</v>
+        <v>0.2632</v>
       </c>
       <c r="AF18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG18">
         <v>0.2367</v>
       </c>
       <c r="AH18">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI18">
-        <v>1.01</v>
+        <v>1.0228</v>
       </c>
       <c r="AJ18" t="b">
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2730,7 +2733,7 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2742,7 +2745,7 @@
         <v>-131</v>
       </c>
       <c r="F19">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2751,13 +2754,13 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N19">
         <v>822698</v>
@@ -2802,10 +2805,10 @@
         <v>4.49</v>
       </c>
       <c r="AB19">
-        <v>0.9271</v>
+        <v>0.9305</v>
       </c>
       <c r="AC19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD19">
         <v>0.2096</v>
@@ -2820,7 +2823,7 @@
         <v>0.2351</v>
       </c>
       <c r="AH19">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI19">
         <v>1.0033</v>
@@ -2829,10 +2832,10 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2843,7 +2846,7 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>5.5</v>
@@ -2855,7 +2858,7 @@
         <v>-115</v>
       </c>
       <c r="F20">
-        <v>5.86</v>
+        <v>5.68</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2864,13 +2867,13 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>5.86</v>
+        <v>5.68</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N20">
         <v>823511</v>
@@ -2915,16 +2918,16 @@
         <v>3.87</v>
       </c>
       <c r="AB20">
-        <v>1.2157</v>
+        <v>1.1508</v>
       </c>
       <c r="AC20" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD20">
-        <v>0.2748</v>
+        <v>0.2592</v>
       </c>
       <c r="AE20">
-        <v>0.2738</v>
+        <v>0.2638</v>
       </c>
       <c r="AF20">
         <v>9</v>
@@ -2933,19 +2936,19 @@
         <v>0.2434</v>
       </c>
       <c r="AH20">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI20">
-        <v>0.9967</v>
+        <v>1.0201</v>
       </c>
       <c r="AJ20" t="b">
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM20">
         <v>0</v>
@@ -2956,7 +2959,7 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2968,7 +2971,7 @@
         <v>113</v>
       </c>
       <c r="F21">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2977,13 +2980,13 @@
         <v>45</v>
       </c>
       <c r="K21">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="L21" t="s">
         <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N21">
         <v>823511</v>
@@ -3028,16 +3031,16 @@
         <v>4.35</v>
       </c>
       <c r="AB21">
-        <v>0.8597</v>
+        <v>0.8726</v>
       </c>
       <c r="AC21" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD21">
-        <v>0.1944</v>
+        <v>0.1965</v>
       </c>
       <c r="AE21">
-        <v>0.1849</v>
+        <v>0.1942</v>
       </c>
       <c r="AF21">
         <v>9</v>
@@ -3046,19 +3049,19 @@
         <v>0.2261</v>
       </c>
       <c r="AH21">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI21">
-        <v>0.9889</v>
+        <v>0.9877</v>
       </c>
       <c r="AJ21" t="b">
         <v>1</v>
       </c>
       <c r="AK21" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL21" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM21">
         <v>0</v>
@@ -3069,7 +3072,7 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22">
         <v>4.5</v>
@@ -3081,7 +3084,7 @@
         <v>-125</v>
       </c>
       <c r="F22">
-        <v>4.64</v>
+        <v>4.28</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -3090,13 +3093,13 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>4.64</v>
+        <v>4.28</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N22">
         <v>822779</v>
@@ -3141,16 +3144,16 @@
         <v>4.12</v>
       </c>
       <c r="AB22">
-        <v>0.8557</v>
+        <v>0.8013</v>
       </c>
       <c r="AC22" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD22">
-        <v>0.1934</v>
+        <v>0.1805</v>
       </c>
       <c r="AE22">
-        <v>0.1835</v>
+        <v>0.1823</v>
       </c>
       <c r="AF22">
         <v>9</v>
@@ -3159,19 +3162,19 @@
         <v>0.215</v>
       </c>
       <c r="AH22">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI22">
-        <v>0.9791</v>
+        <v>0.9641</v>
       </c>
       <c r="AJ22" t="b">
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL22" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM22">
         <v>0</v>
@@ -3182,10 +3185,10 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23">
-        <v>4.07</v>
+        <v>3.86</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -3194,13 +3197,13 @@
         <v>45</v>
       </c>
       <c r="K23">
-        <v>4.07</v>
+        <v>3.86</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N23">
         <v>822779</v>
@@ -3245,16 +3248,16 @@
         <v>4.16</v>
       </c>
       <c r="AB23">
-        <v>0.829</v>
+        <v>0.8128</v>
       </c>
       <c r="AC23" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD23">
-        <v>0.1874</v>
+        <v>0.1831</v>
       </c>
       <c r="AE23">
-        <v>0.1897</v>
+        <v>0.1879</v>
       </c>
       <c r="AF23">
         <v>9</v>
@@ -3263,19 +3266,19 @@
         <v>0.2181</v>
       </c>
       <c r="AH23">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI23">
-        <v>0.9631</v>
+        <v>0.933</v>
       </c>
       <c r="AJ23" t="b">
         <v>1</v>
       </c>
       <c r="AK23" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL23" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM23">
         <v>0</v>
@@ -3286,10 +3289,10 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F24">
-        <v>3.75</v>
+        <v>4.29</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3298,13 +3301,13 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>3.75</v>
+        <v>4.29</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N24">
         <v>824883</v>
@@ -3349,16 +3352,16 @@
         <v>3.89</v>
       </c>
       <c r="AB24">
-        <v>1.0033</v>
+        <v>1.1317</v>
       </c>
       <c r="AC24" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="AD24">
-        <v>0.2268</v>
+        <v>0.2549</v>
       </c>
       <c r="AE24">
-        <v>0.2191</v>
+        <v>0.2198</v>
       </c>
       <c r="AF24">
         <v>9</v>
@@ -3367,19 +3370,19 @@
         <v>0.2094</v>
       </c>
       <c r="AH24">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI24">
-        <v>1.016</v>
+        <v>1.0317</v>
       </c>
       <c r="AJ24" t="b">
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AL24" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AM24">
         <v>0</v>
@@ -3390,7 +3393,7 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -3402,7 +3405,7 @@
         <v>-140</v>
       </c>
       <c r="F25">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3411,13 +3414,13 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>5.88</v>
+        <v>5.9</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N25">
         <v>824883</v>
@@ -3462,10 +3465,10 @@
         <v>4.24</v>
       </c>
       <c r="AB25">
-        <v>1.1171</v>
+        <v>1.1212</v>
       </c>
       <c r="AC25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD25">
         <v>0.2525</v>
@@ -3480,7 +3483,7 @@
         <v>0.2243</v>
       </c>
       <c r="AH25">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI25">
         <v>0.9975</v>
@@ -3489,10 +3492,10 @@
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM25">
         <v>0</v>
@@ -3503,7 +3506,7 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3515,7 +3518,7 @@
         <v>-155</v>
       </c>
       <c r="F26">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3524,13 +3527,13 @@
         <v>45</v>
       </c>
       <c r="K26">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="L26" t="s">
         <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N26">
         <v>824562</v>
@@ -3575,10 +3578,10 @@
         <v>4.49</v>
       </c>
       <c r="AB26">
-        <v>0.9843</v>
+        <v>0.9879</v>
       </c>
       <c r="AC26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD26">
         <v>0.2225</v>
@@ -3593,7 +3596,7 @@
         <v>0.2371</v>
       </c>
       <c r="AH26">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI26">
         <v>1.0267</v>
@@ -3602,10 +3605,10 @@
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM26">
         <v>0</v>
@@ -3616,7 +3619,7 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C27">
         <v>5.5</v>
@@ -3628,7 +3631,7 @@
         <v>-107</v>
       </c>
       <c r="F27">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3637,13 +3640,13 @@
         <v>45</v>
       </c>
       <c r="K27">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N27">
         <v>824562</v>
@@ -3688,10 +3691,10 @@
         <v>4.45</v>
       </c>
       <c r="AB27">
-        <v>1.1139</v>
+        <v>1.118</v>
       </c>
       <c r="AC27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD27">
         <v>0.2518</v>
@@ -3706,7 +3709,7 @@
         <v>0.2555</v>
       </c>
       <c r="AH27">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI27">
         <v>1.0521</v>
@@ -3715,10 +3718,10 @@
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM27">
         <v>0</v>
@@ -3729,7 +3732,7 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F28">
         <v>1.63</v>
@@ -3747,13 +3750,13 @@
         <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N28">
         <v>823916</v>
       </c>
       <c r="O28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P28">
         <v>1.7</v>
@@ -3792,10 +3795,10 @@
         <v>4.05</v>
       </c>
       <c r="AB28">
-        <v>1.2457</v>
+        <v>1.2503</v>
       </c>
       <c r="AC28" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD28">
         <v>0.2816</v>
@@ -3810,7 +3813,7 @@
         <v>0.1984</v>
       </c>
       <c r="AH28">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI28">
         <v>1.0072</v>
@@ -3819,10 +3822,10 @@
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM28">
         <v>0</v>
@@ -3833,7 +3836,7 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29">
         <v>4.5</v>
@@ -3845,7 +3848,7 @@
         <v>-166</v>
       </c>
       <c r="F29">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="H29" t="s">
         <v>45</v>
@@ -3854,13 +3857,13 @@
         <v>45</v>
       </c>
       <c r="K29">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="L29" t="s">
         <v>46</v>
       </c>
       <c r="M29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N29">
         <v>823916</v>
@@ -3905,10 +3908,10 @@
         <v>4.23</v>
       </c>
       <c r="AB29">
-        <v>0.924</v>
+        <v>0.9274</v>
       </c>
       <c r="AC29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD29">
         <v>0.2089</v>
@@ -3923,7 +3926,7 @@
         <v>0.2142</v>
       </c>
       <c r="AH29">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI29">
         <v>0.9653</v>
@@ -3932,10 +3935,10 @@
         <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -3946,7 +3949,7 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C30">
         <v>3.5</v>
@@ -3958,7 +3961,7 @@
         <v>-119</v>
       </c>
       <c r="F30">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="H30" t="s">
         <v>45</v>
@@ -3967,13 +3970,13 @@
         <v>45</v>
       </c>
       <c r="K30">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="L30" t="s">
         <v>46</v>
       </c>
       <c r="M30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N30">
         <v>823994</v>
@@ -4018,10 +4021,10 @@
         <v>4.2</v>
       </c>
       <c r="AB30">
-        <v>1.1892</v>
+        <v>1.1935</v>
       </c>
       <c r="AC30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD30">
         <v>0.2688</v>
@@ -4036,7 +4039,7 @@
         <v>0.2508</v>
       </c>
       <c r="AH30">
-        <v>0.2261</v>
+        <v>0.2252</v>
       </c>
       <c r="AI30">
         <v>1.0161</v>
@@ -4045,10 +4048,10 @@
         <v>1</v>
       </c>
       <c r="AK30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AL30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AM30">
         <v>0</v>
@@ -4059,7 +4062,7 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C31">
         <v>5.5</v>
@@ -4080,7 +4083,7 @@
         <v>45</v>
       </c>
       <c r="M31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N31" t="s">
         <v>45</v>
@@ -4109,7 +4112,7 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -4130,7 +4133,7 @@
         <v>45</v>
       </c>
       <c r="M32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N32" t="s">
         <v>45</v>
@@ -4159,7 +4162,7 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -4180,7 +4183,7 @@
         <v>45</v>
       </c>
       <c r="M33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N33" t="s">
         <v>45</v>

--- a/data/k-props/2026-08-12.xlsx
+++ b/data/k-props/2026-08-12.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -193,9 +193,6 @@
     <t>Jack Perkins</t>
   </si>
   <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
     <t>Ryan Feltner</t>
   </si>
   <si>
@@ -238,73 +235,73 @@
     <t>Cleveland Guardians @ Detroit Tigers</t>
   </si>
   <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Carmen Mlodzinski</t>
+  </si>
+  <si>
+    <t>Pittsburgh Pirates @ Miami Marlins</t>
+  </si>
+  <si>
+    <t>Janson Junk</t>
+  </si>
+  <si>
+    <t>David Peterson</t>
+  </si>
+  <si>
+    <t>Chicago Cubs @ Washington Nationals</t>
+  </si>
+  <si>
+    <t>Bryce Miller</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ New York Yankees</t>
+  </si>
+  <si>
+    <t>Will Warren</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Zac Thornton</t>
+  </si>
+  <si>
+    <t>New York Mets @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Cincinnati Reds @ Chicago White Sox</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Carmen Mlodzinski</t>
-  </si>
-  <si>
-    <t>Pittsburgh Pirates @ Miami Marlins</t>
-  </si>
-  <si>
-    <t>Janson Junk</t>
-  </si>
-  <si>
-    <t>David Peterson</t>
-  </si>
-  <si>
-    <t>Chicago Cubs @ Washington Nationals</t>
-  </si>
-  <si>
-    <t>Bryce Miller</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ New York Yankees</t>
-  </si>
-  <si>
-    <t>Will Warren</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Zac Thornton</t>
-  </si>
-  <si>
-    <t>New York Mets @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Cincinnati Reds @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Daniel Lynch IV</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>Eric Lauer</t>
@@ -917,7 +914,7 @@
         <v>4.29</v>
       </c>
       <c r="AB2">
-        <v>0.8743</v>
+        <v>0.8741</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
@@ -932,10 +929,10 @@
         <v>9</v>
       </c>
       <c r="AG2">
-        <v>0.2101</v>
+        <v>0.2096</v>
       </c>
       <c r="AH2">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI2">
         <v>0.9518</v>
@@ -1030,7 +1027,7 @@
         <v>4.25</v>
       </c>
       <c r="AB3">
-        <v>1.1981</v>
+        <v>1.1979</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
@@ -1045,10 +1042,10 @@
         <v>9</v>
       </c>
       <c r="AG3">
-        <v>0.2379</v>
+        <v>0.2376</v>
       </c>
       <c r="AH3">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI3">
         <v>1.0698</v>
@@ -1083,7 +1080,7 @@
         <v>134</v>
       </c>
       <c r="F4">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1092,7 +1089,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="L4" t="s">
         <v>46</v>
@@ -1107,7 +1104,7 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -1119,31 +1116,31 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>0.3036</v>
+        <v>0.3018</v>
       </c>
       <c r="U4">
-        <v>0.3038</v>
+        <v>0.2988</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="X4">
-        <v>0.3043</v>
+        <v>0.2929</v>
       </c>
       <c r="Y4">
-        <v>0.315</v>
+        <v>0.331</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="AB4">
-        <v>0.8975</v>
+        <v>0.8973</v>
       </c>
       <c r="AC4" t="s">
         <v>49</v>
@@ -1158,10 +1155,10 @@
         <v>9</v>
       </c>
       <c r="AG4">
-        <v>0.2126</v>
+        <v>0.2128</v>
       </c>
       <c r="AH4">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI4">
         <v>0.9321</v>
@@ -1256,7 +1253,7 @@
         <v>4.24</v>
       </c>
       <c r="AB5">
-        <v>0.8055</v>
+        <v>0.8053</v>
       </c>
       <c r="AC5" t="s">
         <v>49</v>
@@ -1274,7 +1271,7 @@
         <v>0.2264</v>
       </c>
       <c r="AH5">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI5">
         <v>0.944</v>
@@ -1309,7 +1306,7 @@
         <v>115</v>
       </c>
       <c r="F6">
-        <v>7.59</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1318,7 +1315,7 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>8.17</v>
+        <v>8.08</v>
       </c>
       <c r="L6" t="s">
         <v>57</v>
@@ -1333,7 +1330,7 @@
         <v>48</v>
       </c>
       <c r="P6">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1345,31 +1342,31 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>0.2679</v>
+        <v>0.2628</v>
       </c>
       <c r="U6">
-        <v>0.2915</v>
+        <v>0.2789</v>
       </c>
       <c r="V6">
         <v>5</v>
       </c>
       <c r="W6">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="X6">
-        <v>0.3402</v>
+        <v>0.307</v>
       </c>
       <c r="Y6">
-        <v>0.327</v>
+        <v>0.363</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AB6">
-        <v>1.2147</v>
+        <v>1.2144</v>
       </c>
       <c r="AC6" t="s">
         <v>49</v>
@@ -1384,10 +1381,10 @@
         <v>9</v>
       </c>
       <c r="AG6">
-        <v>0.2171</v>
+        <v>0.2168</v>
       </c>
       <c r="AH6">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI6">
         <v>1.0849</v>
@@ -1422,7 +1419,7 @@
         <v>-147</v>
       </c>
       <c r="F7">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1431,7 +1428,7 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1443,10 +1440,10 @@
         <v>824967</v>
       </c>
       <c r="O7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="P7">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -1458,31 +1455,31 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>0.2556</v>
+        <v>0.25</v>
       </c>
       <c r="U7">
-        <v>0.2419</v>
+        <v>0.2308</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="X7">
-        <v>0.2128</v>
+        <v>0.1964</v>
       </c>
       <c r="Y7">
-        <v>0.32</v>
+        <v>0.359</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="AB7">
-        <v>0.9181</v>
+        <v>0.9179</v>
       </c>
       <c r="AC7" t="s">
         <v>49</v>
@@ -1497,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="AG7">
-        <v>0.192</v>
+        <v>0.1905</v>
       </c>
       <c r="AH7">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI7">
         <v>0.88</v>
@@ -1523,7 +1520,7 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1535,7 +1532,7 @@
         <v>-156</v>
       </c>
       <c r="F8">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="s">
         <v>45</v>
@@ -1544,13 +1541,13 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="L8" t="s">
         <v>46</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N8">
         <v>825047</v>
@@ -1571,31 +1568,31 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>0.1648</v>
+        <v>0.1597</v>
       </c>
       <c r="U8">
-        <v>0.1527</v>
+        <v>0.1458</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X8">
-        <v>0.1316</v>
+        <v>0.1217</v>
       </c>
       <c r="Y8">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="AB8">
-        <v>0.8538</v>
+        <v>0.8536</v>
       </c>
       <c r="AC8" t="s">
         <v>49</v>
@@ -1613,7 +1610,7 @@
         <v>0.2002</v>
       </c>
       <c r="AH8">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI8">
         <v>0.88</v>
@@ -1636,7 +1633,7 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>4.5</v>
@@ -1648,7 +1645,7 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1657,13 +1654,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N9">
         <v>825047</v>
@@ -1684,31 +1681,31 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>0.1541</v>
+        <v>0.1513</v>
       </c>
       <c r="U9">
-        <v>0.1683</v>
+        <v>0.1621</v>
       </c>
       <c r="V9">
         <v>5</v>
       </c>
       <c r="W9">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="X9">
-        <v>0.1944</v>
+        <v>0.1818</v>
       </c>
       <c r="Y9">
-        <v>0.351</v>
+        <v>0.355</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>4.33</v>
+        <v>4.34</v>
       </c>
       <c r="AB9">
-        <v>1.2317</v>
+        <v>1.2314</v>
       </c>
       <c r="AC9" t="s">
         <v>49</v>
@@ -1723,10 +1720,10 @@
         <v>8</v>
       </c>
       <c r="AG9">
-        <v>0.2166</v>
+        <v>0.2159</v>
       </c>
       <c r="AH9">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI9">
         <v>1.0549</v>
@@ -1749,10 +1746,10 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1761,19 +1758,19 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="L10" t="s">
         <v>46</v>
       </c>
       <c r="M10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N10">
         <v>823187</v>
       </c>
       <c r="O10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P10">
         <v>1</v>
@@ -1788,16 +1785,31 @@
         <v>0</v>
       </c>
       <c r="T10">
-        <v>0.1852</v>
+        <v>0.1864</v>
       </c>
       <c r="U10">
-        <v>0.1852</v>
+        <v>0.1876</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>4</v>
+      </c>
+      <c r="X10">
+        <v>0.25</v>
+      </c>
+      <c r="Y10">
+        <v>0.02</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="AB10">
-        <v>1.2122</v>
+        <v>1.2119</v>
       </c>
       <c r="AC10" t="s">
         <v>49</v>
@@ -1815,7 +1827,7 @@
         <v>0.2341</v>
       </c>
       <c r="AH10">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI10">
         <v>1.0778</v>
@@ -1838,10 +1850,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="H11" t="s">
         <v>45</v>
@@ -1850,19 +1862,19 @@
         <v>45</v>
       </c>
       <c r="K11">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="L11" t="s">
         <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N11">
         <v>823187</v>
       </c>
       <c r="O11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P11">
         <v>4</v>
@@ -1901,7 +1913,7 @@
         <v>4.19</v>
       </c>
       <c r="AB11">
-        <v>1.2122</v>
+        <v>1.2119</v>
       </c>
       <c r="AC11" t="s">
         <v>49</v>
@@ -1916,10 +1928,10 @@
         <v>9</v>
       </c>
       <c r="AG11">
-        <v>0.2015</v>
+        <v>0.2016</v>
       </c>
       <c r="AH11">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI11">
         <v>0.9583</v>
@@ -1942,7 +1954,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12">
         <v>2.5</v>
@@ -1954,7 +1966,7 @@
         <v>140</v>
       </c>
       <c r="F12">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1963,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N12">
         <v>823187</v>
@@ -1978,7 +1990,7 @@
         <v>48</v>
       </c>
       <c r="P12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1990,31 +2002,31 @@
         <v>4</v>
       </c>
       <c r="T12">
-        <v>0.1533</v>
+        <v>0.158</v>
       </c>
       <c r="U12">
-        <v>0.1763</v>
+        <v>0.1817</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="X12">
-        <v>0.2472</v>
+        <v>0.2529</v>
       </c>
       <c r="Y12">
-        <v>0.308</v>
+        <v>0.303</v>
       </c>
       <c r="Z12" t="b">
         <v>1</v>
       </c>
       <c r="AA12">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="AB12">
-        <v>0.8555</v>
+        <v>0.8553</v>
       </c>
       <c r="AC12" t="s">
         <v>49</v>
@@ -2029,10 +2041,10 @@
         <v>9</v>
       </c>
       <c r="AG12">
-        <v>0.2163</v>
+        <v>0.2166</v>
       </c>
       <c r="AH12">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI12">
         <v>0.8914</v>
@@ -2055,7 +2067,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -2067,7 +2079,7 @@
         <v>110</v>
       </c>
       <c r="F13">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="H13" t="s">
         <v>45</v>
@@ -2076,13 +2088,13 @@
         <v>45</v>
       </c>
       <c r="K13">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="L13" t="s">
         <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N13">
         <v>823263</v>
@@ -2091,7 +2103,7 @@
         <v>48</v>
       </c>
       <c r="P13">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -2103,31 +2115,31 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>0.2303</v>
+        <v>0.2286</v>
       </c>
       <c r="U13">
-        <v>0.2302</v>
+        <v>0.2284</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="X13">
-        <v>0.2301</v>
+        <v>0.2281</v>
       </c>
       <c r="Y13">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="AB13">
-        <v>0.7237</v>
+        <v>0.7235</v>
       </c>
       <c r="AC13" t="s">
         <v>49</v>
@@ -2142,10 +2154,10 @@
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>0.2193</v>
+        <v>0.2191</v>
       </c>
       <c r="AH13">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI13">
         <v>0.9807</v>
@@ -2168,7 +2180,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -2180,7 +2192,7 @@
         <v>127</v>
       </c>
       <c r="F14">
-        <v>4.68</v>
+        <v>4.72</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -2189,13 +2201,13 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>4.68</v>
+        <v>4.72</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N14">
         <v>823263</v>
@@ -2204,7 +2216,7 @@
         <v>48</v>
       </c>
       <c r="P14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -2216,22 +2228,22 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>0.203</v>
+        <v>0.204</v>
       </c>
       <c r="U14">
-        <v>0.2006</v>
+        <v>0.2051</v>
       </c>
       <c r="V14">
         <v>5</v>
       </c>
       <c r="W14">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="X14">
-        <v>0.1966</v>
+        <v>0.2072</v>
       </c>
       <c r="Y14">
-        <v>0.369</v>
+        <v>0.357</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2240,7 +2252,7 @@
         <v>4.21</v>
       </c>
       <c r="AB14">
-        <v>1.0511</v>
+        <v>1.0509</v>
       </c>
       <c r="AC14" t="s">
         <v>49</v>
@@ -2258,7 +2270,7 @@
         <v>0.2157</v>
       </c>
       <c r="AH14">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI14">
         <v>0.9557</v>
@@ -2281,7 +2293,7 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2293,7 +2305,7 @@
         <v>-150</v>
       </c>
       <c r="F15">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2302,13 +2314,13 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N15">
         <v>824241</v>
@@ -2353,37 +2365,37 @@
         <v>4.09</v>
       </c>
       <c r="AB15">
-        <v>0.8817</v>
+        <v>0.9048</v>
       </c>
       <c r="AC15" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="AD15">
-        <v>0.1986</v>
+        <v>0.2039</v>
       </c>
       <c r="AE15">
-        <v>0.1994</v>
+        <v>0.206</v>
       </c>
       <c r="AF15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>0.2263</v>
       </c>
       <c r="AH15">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI15">
-        <v>0.9855</v>
+        <v>0.9824</v>
       </c>
       <c r="AJ15" t="b">
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2394,7 +2406,7 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2406,7 +2418,7 @@
         <v>-122</v>
       </c>
       <c r="F16">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2415,13 +2427,13 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N16">
         <v>824241</v>
@@ -2466,7 +2478,7 @@
         <v>4.38</v>
       </c>
       <c r="AB16">
-        <v>0.825</v>
+        <v>0.8248</v>
       </c>
       <c r="AC16" t="s">
         <v>49</v>
@@ -2484,7 +2496,7 @@
         <v>0.2295</v>
       </c>
       <c r="AH16">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI16">
         <v>0.8885</v>
@@ -2507,7 +2519,7 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2534,7 +2546,7 @@
         <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N17">
         <v>823833</v>
@@ -2579,7 +2591,7 @@
         <v>4.29</v>
       </c>
       <c r="AB17">
-        <v>1.1519</v>
+        <v>1.1516</v>
       </c>
       <c r="AC17" t="s">
         <v>49</v>
@@ -2597,7 +2609,7 @@
         <v>0.2104</v>
       </c>
       <c r="AH17">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI17">
         <v>0.9334</v>
@@ -2620,7 +2632,7 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2647,7 +2659,7 @@
         <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N18">
         <v>823833</v>
@@ -2692,7 +2704,7 @@
         <v>4.29</v>
       </c>
       <c r="AB18">
-        <v>1.0365</v>
+        <v>1.0363</v>
       </c>
       <c r="AC18" t="s">
         <v>49</v>
@@ -2710,7 +2722,7 @@
         <v>0.2367</v>
       </c>
       <c r="AH18">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI18">
         <v>1.0228</v>
@@ -2733,7 +2745,7 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2745,7 +2757,7 @@
         <v>-131</v>
       </c>
       <c r="F19">
-        <v>3.82</v>
+        <v>4.14</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2754,13 +2766,13 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>3.82</v>
+        <v>4.14</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N19">
         <v>822698</v>
@@ -2805,16 +2817,16 @@
         <v>4.49</v>
       </c>
       <c r="AB19">
-        <v>0.9305</v>
+        <v>0.992</v>
       </c>
       <c r="AC19" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="AD19">
-        <v>0.2096</v>
+        <v>0.2235</v>
       </c>
       <c r="AE19">
-        <v>0.2156</v>
+        <v>0.2204</v>
       </c>
       <c r="AF19">
         <v>9</v>
@@ -2823,19 +2835,19 @@
         <v>0.2351</v>
       </c>
       <c r="AH19">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI19">
-        <v>1.0033</v>
+        <v>1.0189</v>
       </c>
       <c r="AJ19" t="b">
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AL19" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2846,7 +2858,7 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>5.5</v>
@@ -2873,7 +2885,7 @@
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N20">
         <v>823511</v>
@@ -2918,7 +2930,7 @@
         <v>3.87</v>
       </c>
       <c r="AB20">
-        <v>1.1508</v>
+        <v>1.1505</v>
       </c>
       <c r="AC20" t="s">
         <v>49</v>
@@ -2936,7 +2948,7 @@
         <v>0.2434</v>
       </c>
       <c r="AH20">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI20">
         <v>1.0201</v>
@@ -2959,7 +2971,7 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2986,7 +2998,7 @@
         <v>46</v>
       </c>
       <c r="M21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N21">
         <v>823511</v>
@@ -3031,7 +3043,7 @@
         <v>4.35</v>
       </c>
       <c r="AB21">
-        <v>0.8726</v>
+        <v>0.8724</v>
       </c>
       <c r="AC21" t="s">
         <v>49</v>
@@ -3049,7 +3061,7 @@
         <v>0.2261</v>
       </c>
       <c r="AH21">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI21">
         <v>0.9877</v>
@@ -3072,7 +3084,7 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <v>4.5</v>
@@ -3099,7 +3111,7 @@
         <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N22">
         <v>822779</v>
@@ -3144,7 +3156,7 @@
         <v>4.12</v>
       </c>
       <c r="AB22">
-        <v>0.8013</v>
+        <v>0.8011</v>
       </c>
       <c r="AC22" t="s">
         <v>49</v>
@@ -3162,7 +3174,7 @@
         <v>0.215</v>
       </c>
       <c r="AH22">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI22">
         <v>0.9641</v>
@@ -3185,7 +3197,7 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F23">
         <v>3.86</v>
@@ -3203,7 +3215,7 @@
         <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N23">
         <v>822779</v>
@@ -3248,7 +3260,7 @@
         <v>4.16</v>
       </c>
       <c r="AB23">
-        <v>0.8128</v>
+        <v>0.8127</v>
       </c>
       <c r="AC23" t="s">
         <v>49</v>
@@ -3266,7 +3278,7 @@
         <v>0.2181</v>
       </c>
       <c r="AH23">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI23">
         <v>0.933</v>
@@ -3289,7 +3301,7 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F24">
         <v>4.29</v>
@@ -3307,7 +3319,7 @@
         <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N24">
         <v>824883</v>
@@ -3352,7 +3364,7 @@
         <v>3.89</v>
       </c>
       <c r="AB24">
-        <v>1.1317</v>
+        <v>1.1314</v>
       </c>
       <c r="AC24" t="s">
         <v>49</v>
@@ -3370,7 +3382,7 @@
         <v>0.2094</v>
       </c>
       <c r="AH24">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI24">
         <v>1.0317</v>
@@ -3393,7 +3405,7 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -3405,7 +3417,7 @@
         <v>-140</v>
       </c>
       <c r="F25">
-        <v>5.9</v>
+        <v>5.77</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3414,13 +3426,13 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>5.9</v>
+        <v>5.77</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N25">
         <v>824883</v>
@@ -3465,37 +3477,37 @@
         <v>4.24</v>
       </c>
       <c r="AB25">
-        <v>1.1212</v>
+        <v>1.0901</v>
       </c>
       <c r="AC25" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="AD25">
-        <v>0.2525</v>
+        <v>0.2456</v>
       </c>
       <c r="AE25">
-        <v>0.2508</v>
+        <v>0.2456</v>
       </c>
       <c r="AF25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG25">
         <v>0.2243</v>
       </c>
       <c r="AH25">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI25">
-        <v>0.9975</v>
+        <v>1.0037</v>
       </c>
       <c r="AJ25" t="b">
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AL25" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AM25">
         <v>0</v>
@@ -3506,7 +3518,7 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -3518,7 +3530,7 @@
         <v>-155</v>
       </c>
       <c r="F26">
-        <v>4.16</v>
+        <v>4.91</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3527,13 +3539,13 @@
         <v>45</v>
       </c>
       <c r="K26">
-        <v>4.16</v>
+        <v>4.91</v>
       </c>
       <c r="L26" t="s">
         <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N26">
         <v>824562</v>
@@ -3578,16 +3590,16 @@
         <v>4.49</v>
       </c>
       <c r="AB26">
-        <v>0.9879</v>
+        <v>1.0718</v>
       </c>
       <c r="AC26" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="AD26">
-        <v>0.2225</v>
+        <v>0.2415</v>
       </c>
       <c r="AE26">
-        <v>0.2425</v>
+        <v>0.2522</v>
       </c>
       <c r="AF26">
         <v>9</v>
@@ -3596,19 +3608,19 @@
         <v>0.2371</v>
       </c>
       <c r="AH26">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI26">
-        <v>1.0267</v>
+        <v>1.1152</v>
       </c>
       <c r="AJ26" t="b">
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AL26" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AM26">
         <v>0</v>
@@ -3619,7 +3631,7 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C27">
         <v>5.5</v>
@@ -3631,7 +3643,7 @@
         <v>-107</v>
       </c>
       <c r="F27">
-        <v>4.79</v>
+        <v>4.71</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3640,13 +3652,13 @@
         <v>45</v>
       </c>
       <c r="K27">
-        <v>4.79</v>
+        <v>4.71</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N27">
         <v>824562</v>
@@ -3691,16 +3703,16 @@
         <v>4.45</v>
       </c>
       <c r="AB27">
-        <v>1.118</v>
+        <v>1.0548</v>
       </c>
       <c r="AC27" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="AD27">
-        <v>0.2518</v>
+        <v>0.2376</v>
       </c>
       <c r="AE27">
-        <v>0.2675</v>
+        <v>0.2691</v>
       </c>
       <c r="AF27">
         <v>9</v>
@@ -3709,19 +3721,19 @@
         <v>0.2555</v>
       </c>
       <c r="AH27">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI27">
-        <v>1.0521</v>
+        <v>1.0959</v>
       </c>
       <c r="AJ27" t="b">
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AL27" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="AM27">
         <v>0</v>
@@ -3732,7 +3744,7 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F28">
         <v>1.63</v>
@@ -3750,13 +3762,13 @@
         <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N28">
         <v>823916</v>
       </c>
       <c r="O28" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P28">
         <v>1.7</v>
@@ -3795,10 +3807,10 @@
         <v>4.05</v>
       </c>
       <c r="AB28">
-        <v>1.2503</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AD28">
         <v>0.2816</v>
@@ -3813,7 +3825,7 @@
         <v>0.1984</v>
       </c>
       <c r="AH28">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI28">
         <v>1.0072</v>
@@ -3822,10 +3834,10 @@
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AL28" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AM28">
         <v>0</v>
@@ -3836,7 +3848,7 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C29">
         <v>4.5</v>
@@ -3863,7 +3875,7 @@
         <v>46</v>
       </c>
       <c r="M29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="N29">
         <v>823916</v>
@@ -3908,10 +3920,10 @@
         <v>4.23</v>
       </c>
       <c r="AB29">
-        <v>0.9274</v>
+        <v>0.9272</v>
       </c>
       <c r="AC29" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AD29">
         <v>0.2089</v>
@@ -3926,7 +3938,7 @@
         <v>0.2142</v>
       </c>
       <c r="AH29">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI29">
         <v>0.9653</v>
@@ -3935,10 +3947,10 @@
         <v>1</v>
       </c>
       <c r="AK29" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AL29" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AM29">
         <v>0</v>
@@ -3949,7 +3961,7 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C30">
         <v>3.5</v>
@@ -3976,7 +3988,7 @@
         <v>46</v>
       </c>
       <c r="M30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N30">
         <v>823994</v>
@@ -4021,10 +4033,10 @@
         <v>4.2</v>
       </c>
       <c r="AB30">
-        <v>1.1935</v>
+        <v>1.1932</v>
       </c>
       <c r="AC30" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AD30">
         <v>0.2688</v>
@@ -4039,7 +4051,7 @@
         <v>0.2508</v>
       </c>
       <c r="AH30">
-        <v>0.2252</v>
+        <v>0.2253</v>
       </c>
       <c r="AI30">
         <v>1.0161</v>
@@ -4048,10 +4060,10 @@
         <v>1</v>
       </c>
       <c r="AK30" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AL30" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AM30">
         <v>0</v>
@@ -4062,7 +4074,7 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>5.5</v>
@@ -4083,7 +4095,7 @@
         <v>45</v>
       </c>
       <c r="M31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N31" t="s">
         <v>45</v>
@@ -4112,7 +4124,7 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32">
         <v>3.5</v>
@@ -4133,7 +4145,7 @@
         <v>45</v>
       </c>
       <c r="M32" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N32" t="s">
         <v>45</v>
@@ -4162,7 +4174,7 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33">
         <v>4.5</v>
@@ -4183,7 +4195,7 @@
         <v>45</v>
       </c>
       <c r="M33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N33" t="s">
         <v>45</v>
